--- a/01-training-center-survey-analysis/data/survey_B_mock.xlsx
+++ b/01-training-center-survey-analysis/data/survey_B_mock.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\airyt\Education-and-User-Experience-Data-Analysis\01-training-center-survey-analysis\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402C7EF0-E989-403F-9881-4F4243106413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="878" windowWidth="21600" windowHeight="11902" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="55">
   <si>
     <t>response_id</t>
   </si>
@@ -38,12 +44,6 @@
   </si>
   <si>
     <t>sat_01</t>
-  </si>
-  <si>
-    <t>flag_low</t>
-  </si>
-  <si>
-    <t>flag_serious</t>
   </si>
   <si>
     <t>text_01</t>
@@ -138,16 +138,80 @@
   <si>
     <t>kf_B</t>
   </si>
+  <si>
+    <t>찾아오는 길 안내가 부족해요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영시간이 자주 바뀌는 것 같아요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이용방법이 직관적이지 않아요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>예약 시스템을 사용하기 어려워요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴식 취할 수 있는 공간이 더 많으면 좋겠어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라운지를 써도 되는지 잘 모르겠어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 다양한 행사를 하면 좋을 것 같아요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문의를 어디다가 해야되는지 모르겠어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안내문이 센터 내 잘 보이는 곳이 붙어 있으면 좋겠어요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출결 시스템이 자꾸 오류 나서 매번 수동으로 확인하는 게 번거롭습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수강생 간의 친목 소음이 라운지에서 너무 크게 들립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그램 난이도 조정이 필요할 것 같아요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영 안내 시각 변경된 거 공지해주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>친절하십니다 ㅎㅎ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상구 쪽에 짐이 쌓여 있어서 안전 문제가 걱정돼요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상담 신청을 남겼는데 운영팀에서 며칠째 확인을 안 하네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -155,8 +219,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -202,17 +273,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,7 +329,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -284,6 +363,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -318,9 +398,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -493,11 +574,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M251"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K251"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="9" max="9" width="23.8125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,19 +615,13 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>368</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -563,28 +641,22 @@
       <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>382</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -604,25 +676,19 @@
       <c r="H3">
         <v>5</v>
       </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>388</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -642,25 +708,19 @@
       <c r="H4">
         <v>4</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>904</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -680,25 +740,19 @@
       <c r="H5">
         <v>5</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
         <v>37</v>
       </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>509</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -718,28 +772,22 @@
       <c r="H6">
         <v>5</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" t="s">
         <v>37</v>
       </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>950</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -759,28 +807,22 @@
       <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="s">
         <v>37</v>
       </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>918</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -800,25 +842,19 @@
       <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
         <v>37</v>
       </c>
-      <c r="M8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -838,25 +874,19 @@
       <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
         <v>37</v>
       </c>
-      <c r="M9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>156</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -876,25 +906,19 @@
       <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="J10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" t="s">
         <v>37</v>
       </c>
-      <c r="M10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>562</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -914,25 +938,19 @@
       <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
         <v>37</v>
       </c>
-      <c r="M11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -952,25 +970,19 @@
       <c r="H12">
         <v>5</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="J12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>994</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -990,25 +1002,19 @@
       <c r="H13">
         <v>5</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="J13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>695</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1028,25 +1034,19 @@
       <c r="H14">
         <v>5</v>
       </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>909</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1066,25 +1066,19 @@
       <c r="H15">
         <v>5</v>
       </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="J15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>521</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1104,25 +1098,19 @@
       <c r="H16">
         <v>5</v>
       </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" t="s">
         <v>37</v>
       </c>
-      <c r="M16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -1142,25 +1130,19 @@
       <c r="H17">
         <v>5</v>
       </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="J17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A18">
         <v>713</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -1180,25 +1162,19 @@
       <c r="H18">
         <v>5</v>
       </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="J18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>776</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -1218,28 +1194,22 @@
       <c r="H19">
         <v>5</v>
       </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>35</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A20">
         <v>902</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -1259,25 +1229,19 @@
       <c r="H20">
         <v>5</v>
       </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="J20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" t="s">
         <v>37</v>
       </c>
-      <c r="M20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A21">
         <v>370</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1297,25 +1261,19 @@
       <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="J21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>337</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -1335,25 +1293,19 @@
       <c r="H22">
         <v>5</v>
       </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="J22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A23">
         <v>543</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -1373,25 +1325,19 @@
       <c r="H23">
         <v>5</v>
       </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="J23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" t="s">
         <v>37</v>
       </c>
-      <c r="M23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A24">
         <v>733</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -1411,28 +1357,22 @@
       <c r="H24">
         <v>5</v>
       </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>1</v>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>35</v>
       </c>
       <c r="K24" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" t="s">
         <v>37</v>
       </c>
-      <c r="M24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A25">
         <v>127</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -1452,25 +1392,22 @@
       <c r="H25">
         <v>5</v>
       </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="I25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>926</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1490,25 +1427,19 @@
       <c r="H26">
         <v>5</v>
       </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="s">
+      <c r="J26" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" t="s">
         <v>37</v>
       </c>
-      <c r="M26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A27">
         <v>617</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -1528,25 +1459,19 @@
       <c r="H27">
         <v>4</v>
       </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="s">
-        <v>37</v>
-      </c>
-      <c r="M27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="J27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A28">
         <v>236</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -1566,25 +1491,19 @@
       <c r="H28">
         <v>5</v>
       </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="s">
-        <v>37</v>
-      </c>
-      <c r="M28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="J28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A29">
         <v>610</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1604,25 +1523,19 @@
       <c r="H29">
         <v>5</v>
       </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="s">
+      <c r="J29" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" t="s">
         <v>37</v>
       </c>
-      <c r="M29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A30">
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -1642,25 +1555,19 @@
       <c r="H30">
         <v>4</v>
       </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="s">
-        <v>37</v>
-      </c>
-      <c r="M30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="J30" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A31">
         <v>419</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -1680,25 +1587,19 @@
       <c r="H31">
         <v>5</v>
       </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
-        <v>37</v>
-      </c>
-      <c r="M31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="J31" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A32">
         <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -1718,25 +1619,19 @@
       <c r="H32">
         <v>5</v>
       </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="J32" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" t="s">
         <v>37</v>
       </c>
-      <c r="M32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A33">
         <v>470</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -1756,25 +1651,19 @@
       <c r="H33">
         <v>5</v>
       </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="s">
+      <c r="J33" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" t="s">
         <v>37</v>
       </c>
-      <c r="M33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A34">
         <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>4</v>
@@ -1794,25 +1683,19 @@
       <c r="H34">
         <v>5</v>
       </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="s">
-        <v>37</v>
-      </c>
-      <c r="M34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="J34" t="s">
+        <v>35</v>
+      </c>
+      <c r="K34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A35">
         <v>885</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -1832,25 +1715,19 @@
       <c r="H35">
         <v>5</v>
       </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="J35" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" t="s">
         <v>37</v>
       </c>
-      <c r="M35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A36">
         <v>871</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -1870,25 +1747,19 @@
       <c r="H36">
         <v>5</v>
       </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="s">
-        <v>37</v>
-      </c>
-      <c r="M36" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="J36" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A37">
         <v>414</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -1908,28 +1779,22 @@
       <c r="H37">
         <v>5</v>
       </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>35</v>
       </c>
       <c r="K37" t="s">
-        <v>17</v>
-      </c>
-      <c r="L37" t="s">
-        <v>37</v>
-      </c>
-      <c r="M37" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A38">
         <v>882</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -1949,25 +1814,22 @@
       <c r="H38">
         <v>5</v>
       </c>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="s">
-        <v>37</v>
-      </c>
-      <c r="M38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="I38" t="s">
+        <v>48</v>
+      </c>
+      <c r="J38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A39">
         <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -1987,25 +1849,19 @@
       <c r="H39">
         <v>5</v>
       </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="J39" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" t="s">
         <v>37</v>
       </c>
-      <c r="M39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A40">
         <v>235</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -2025,28 +1881,22 @@
       <c r="H40">
         <v>5</v>
       </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
+      <c r="I40" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" t="s">
+        <v>35</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A41">
         <v>570</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -2066,25 +1916,19 @@
       <c r="H41">
         <v>4</v>
       </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="s">
-        <v>37</v>
-      </c>
-      <c r="M41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="J41" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A42">
         <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -2104,25 +1948,19 @@
       <c r="H42">
         <v>5</v>
       </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="s">
-        <v>37</v>
-      </c>
-      <c r="M42" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="J42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A43">
         <v>649</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -2142,28 +1980,22 @@
       <c r="H43">
         <v>5</v>
       </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
+      <c r="I43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>35</v>
       </c>
       <c r="K43" t="s">
-        <v>22</v>
-      </c>
-      <c r="L43" t="s">
         <v>37</v>
       </c>
-      <c r="M43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A44">
         <v>282</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -2183,25 +2015,19 @@
       <c r="H44">
         <v>5</v>
       </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" t="s">
-        <v>37</v>
-      </c>
-      <c r="M44" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="J44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A45">
         <v>643</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -2221,25 +2047,19 @@
       <c r="H45">
         <v>5</v>
       </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="s">
-        <v>37</v>
-      </c>
-      <c r="M45" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="J45" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A46">
         <v>723</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -2259,28 +2079,22 @@
       <c r="H46">
         <v>4</v>
       </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>35</v>
       </c>
       <c r="K46" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46" t="s">
-        <v>37</v>
-      </c>
-      <c r="M46" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A47">
         <v>821</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -2300,28 +2114,22 @@
       <c r="H47">
         <v>5</v>
       </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>35</v>
       </c>
       <c r="K47" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" t="s">
         <v>37</v>
       </c>
-      <c r="M47" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A48">
         <v>708</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -2341,25 +2149,19 @@
       <c r="H48">
         <v>4</v>
       </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="s">
-        <v>37</v>
-      </c>
-      <c r="M48" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="J48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A49">
         <v>130</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -2379,25 +2181,22 @@
       <c r="H49">
         <v>5</v>
       </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="s">
-        <v>37</v>
-      </c>
-      <c r="M49" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="I49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J49" t="s">
+        <v>35</v>
+      </c>
+      <c r="K49" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A50">
         <v>631</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -2417,25 +2216,19 @@
       <c r="H50">
         <v>5</v>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="s">
+      <c r="J50" t="s">
+        <v>35</v>
+      </c>
+      <c r="K50" t="s">
         <v>37</v>
       </c>
-      <c r="M50" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A51">
         <v>320</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C51">
         <v>5</v>
@@ -2455,25 +2248,19 @@
       <c r="H51">
         <v>4</v>
       </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="s">
-        <v>37</v>
-      </c>
-      <c r="M51" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="J51" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A52">
         <v>314</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C52">
         <v>4</v>
@@ -2493,25 +2280,19 @@
       <c r="H52">
         <v>4</v>
       </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="s">
-        <v>37</v>
-      </c>
-      <c r="M52" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="J52" t="s">
+        <v>35</v>
+      </c>
+      <c r="K52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A53">
         <v>616</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C53">
         <v>5</v>
@@ -2531,25 +2312,19 @@
       <c r="H53">
         <v>5</v>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="s">
-        <v>37</v>
-      </c>
-      <c r="M53" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="J53" t="s">
+        <v>35</v>
+      </c>
+      <c r="K53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A54">
         <v>628</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -2569,25 +2344,19 @@
       <c r="H54">
         <v>5</v>
       </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="s">
-        <v>37</v>
-      </c>
-      <c r="M54" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="J54" t="s">
+        <v>35</v>
+      </c>
+      <c r="K54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A55">
         <v>622</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -2607,25 +2376,19 @@
       <c r="H55">
         <v>5</v>
       </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" t="s">
-        <v>37</v>
-      </c>
-      <c r="M55" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="J55" t="s">
+        <v>35</v>
+      </c>
+      <c r="K55" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A56">
         <v>493</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C56">
         <v>5</v>
@@ -2645,25 +2408,19 @@
       <c r="H56">
         <v>5</v>
       </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
+      <c r="J56" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56" t="s">
         <v>37</v>
       </c>
-      <c r="M56" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A57">
         <v>279</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C57">
         <v>4</v>
@@ -2683,25 +2440,19 @@
       <c r="H57">
         <v>5</v>
       </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" t="s">
-        <v>37</v>
-      </c>
-      <c r="M57" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="J57" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A58">
         <v>199</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C58">
         <v>5</v>
@@ -2721,25 +2472,19 @@
       <c r="H58">
         <v>5</v>
       </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" t="s">
-        <v>37</v>
-      </c>
-      <c r="M58" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+      <c r="J58" t="s">
+        <v>35</v>
+      </c>
+      <c r="K58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A59">
         <v>298</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -2759,25 +2504,19 @@
       <c r="H59">
         <v>5</v>
       </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="s">
-        <v>37</v>
-      </c>
-      <c r="M59" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+      <c r="J59" t="s">
+        <v>35</v>
+      </c>
+      <c r="K59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A60">
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2797,25 +2536,19 @@
       <c r="H60">
         <v>5</v>
       </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" t="s">
+      <c r="J60" t="s">
+        <v>35</v>
+      </c>
+      <c r="K60" t="s">
         <v>37</v>
       </c>
-      <c r="M60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A61">
         <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C61">
         <v>5</v>
@@ -2835,28 +2568,22 @@
       <c r="H61">
         <v>5</v>
       </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
+      <c r="I61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s">
+        <v>35</v>
       </c>
       <c r="K61" t="s">
-        <v>22</v>
-      </c>
-      <c r="L61" t="s">
-        <v>37</v>
-      </c>
-      <c r="M61" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A62">
         <v>49</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2876,25 +2603,19 @@
       <c r="H62">
         <v>4</v>
       </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" t="s">
+      <c r="J62" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62" t="s">
         <v>37</v>
       </c>
-      <c r="M62" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A63">
         <v>141</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -2914,25 +2635,19 @@
       <c r="H63">
         <v>4</v>
       </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
-        <v>37</v>
-      </c>
-      <c r="M63" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="J63" t="s">
+        <v>35</v>
+      </c>
+      <c r="K63" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A64">
         <v>906</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C64">
         <v>4</v>
@@ -2952,25 +2667,19 @@
       <c r="H64">
         <v>5</v>
       </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" t="s">
-        <v>37</v>
-      </c>
-      <c r="M64" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="J64" t="s">
+        <v>35</v>
+      </c>
+      <c r="K64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A65">
         <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -2990,28 +2699,22 @@
       <c r="H65">
         <v>5</v>
       </c>
-      <c r="I65" t="b">
-        <v>0</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
+      <c r="I65" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s">
+        <v>35</v>
       </c>
       <c r="K65" t="s">
-        <v>24</v>
-      </c>
-      <c r="L65" t="s">
-        <v>37</v>
-      </c>
-      <c r="M65" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A66">
         <v>280</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -3031,25 +2734,19 @@
       <c r="H66">
         <v>4</v>
       </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" t="s">
-        <v>37</v>
-      </c>
-      <c r="M66" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="J66" t="s">
+        <v>35</v>
+      </c>
+      <c r="K66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A67">
         <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C67">
         <v>5</v>
@@ -3069,25 +2766,19 @@
       <c r="H67">
         <v>4</v>
       </c>
-      <c r="I67" t="b">
-        <v>0</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
-        <v>37</v>
-      </c>
-      <c r="M67" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="J67" t="s">
+        <v>35</v>
+      </c>
+      <c r="K67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A68">
         <v>533</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C68">
         <v>5</v>
@@ -3107,25 +2798,22 @@
       <c r="H68">
         <v>4</v>
       </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>37</v>
-      </c>
-      <c r="M68" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="I68" t="s">
+        <v>50</v>
+      </c>
+      <c r="J68" t="s">
+        <v>35</v>
+      </c>
+      <c r="K68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A69">
         <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C69">
         <v>5</v>
@@ -3145,25 +2833,19 @@
       <c r="H69">
         <v>5</v>
       </c>
-      <c r="I69" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="L69" t="s">
-        <v>37</v>
-      </c>
-      <c r="M69" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="J69" t="s">
+        <v>35</v>
+      </c>
+      <c r="K69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A70">
         <v>865</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C70">
         <v>5</v>
@@ -3183,25 +2865,22 @@
       <c r="H70">
         <v>4</v>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>37</v>
-      </c>
-      <c r="M70" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="I70" t="s">
+        <v>51</v>
+      </c>
+      <c r="J70" t="s">
+        <v>35</v>
+      </c>
+      <c r="K70" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A71">
         <v>754</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C71">
         <v>4</v>
@@ -3221,25 +2900,19 @@
       <c r="H71">
         <v>5</v>
       </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
-        <v>37</v>
-      </c>
-      <c r="M71" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="J71" t="s">
+        <v>35</v>
+      </c>
+      <c r="K71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A72">
         <v>467</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C72">
         <v>5</v>
@@ -3259,25 +2932,19 @@
       <c r="H72">
         <v>5</v>
       </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" t="s">
-        <v>37</v>
-      </c>
-      <c r="M72" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="J72" t="s">
+        <v>35</v>
+      </c>
+      <c r="K72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A73">
         <v>472</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -3297,28 +2964,22 @@
       <c r="H73">
         <v>5</v>
       </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="b">
-        <v>1</v>
+      <c r="I73" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" t="s">
+        <v>35</v>
       </c>
       <c r="K73" t="s">
-        <v>25</v>
-      </c>
-      <c r="L73" t="s">
-        <v>37</v>
-      </c>
-      <c r="M73" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A74">
         <v>462</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74">
         <v>4</v>
@@ -3338,25 +2999,19 @@
       <c r="H74">
         <v>5</v>
       </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" t="s">
+      <c r="J74" t="s">
+        <v>35</v>
+      </c>
+      <c r="K74" t="s">
         <v>37</v>
       </c>
-      <c r="M74" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A75">
         <v>899</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -3376,25 +3031,19 @@
       <c r="H75">
         <v>5</v>
       </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" t="s">
-        <v>37</v>
-      </c>
-      <c r="M75" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="J75" t="s">
+        <v>35</v>
+      </c>
+      <c r="K75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A76">
         <v>339</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C76">
         <v>5</v>
@@ -3414,28 +3063,22 @@
       <c r="H76">
         <v>5</v>
       </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
+      <c r="I76" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" t="s">
+        <v>35</v>
       </c>
       <c r="K76" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" t="s">
-        <v>37</v>
-      </c>
-      <c r="M76" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A77">
         <v>793</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C77">
         <v>4</v>
@@ -3455,25 +3098,19 @@
       <c r="H77">
         <v>5</v>
       </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77" t="s">
-        <v>37</v>
-      </c>
-      <c r="M77" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
+      <c r="J77" t="s">
+        <v>35</v>
+      </c>
+      <c r="K77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A78">
         <v>515</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C78">
         <v>5</v>
@@ -3493,25 +3130,19 @@
       <c r="H78">
         <v>5</v>
       </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" t="s">
+      <c r="J78" t="s">
+        <v>35</v>
+      </c>
+      <c r="K78" t="s">
         <v>37</v>
       </c>
-      <c r="M78" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A79">
         <v>915</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C79">
         <v>5</v>
@@ -3531,25 +3162,19 @@
       <c r="H79">
         <v>5</v>
       </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" t="s">
+      <c r="J79" t="s">
+        <v>35</v>
+      </c>
+      <c r="K79" t="s">
         <v>37</v>
       </c>
-      <c r="M79" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A80">
         <v>941</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C80">
         <v>5</v>
@@ -3569,28 +3194,22 @@
       <c r="H80">
         <v>5</v>
       </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
+      <c r="I80" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" t="s">
+        <v>35</v>
       </c>
       <c r="K80" t="s">
-        <v>27</v>
-      </c>
-      <c r="L80" t="s">
         <v>37</v>
       </c>
-      <c r="M80" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A81">
         <v>752</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C81">
         <v>5</v>
@@ -3610,25 +3229,19 @@
       <c r="H81">
         <v>5</v>
       </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="L81" t="s">
-        <v>37</v>
-      </c>
-      <c r="M81" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="J81" t="s">
+        <v>35</v>
+      </c>
+      <c r="K81" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A82">
         <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C82">
         <v>5</v>
@@ -3648,25 +3261,19 @@
       <c r="H82">
         <v>5</v>
       </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="L82" t="s">
-        <v>37</v>
-      </c>
-      <c r="M82" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="J82" t="s">
+        <v>35</v>
+      </c>
+      <c r="K82" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A83">
         <v>514</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C83">
         <v>5</v>
@@ -3686,25 +3293,19 @@
       <c r="H83">
         <v>5</v>
       </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>37</v>
-      </c>
-      <c r="M83" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="J83" t="s">
+        <v>35</v>
+      </c>
+      <c r="K83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A84">
         <v>977</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C84">
         <v>4</v>
@@ -3724,28 +3325,22 @@
       <c r="H84">
         <v>5</v>
       </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
+      <c r="I84" t="s">
+        <v>26</v>
+      </c>
+      <c r="J84" t="s">
+        <v>35</v>
       </c>
       <c r="K84" t="s">
-        <v>28</v>
-      </c>
-      <c r="L84" t="s">
         <v>37</v>
       </c>
-      <c r="M84" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A85">
         <v>200</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C85">
         <v>5</v>
@@ -3765,25 +3360,19 @@
       <c r="H85">
         <v>5</v>
       </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="L85" t="s">
-        <v>37</v>
-      </c>
-      <c r="M85" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="J85" t="s">
+        <v>35</v>
+      </c>
+      <c r="K85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A86">
         <v>647</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C86">
         <v>5</v>
@@ -3803,25 +3392,19 @@
       <c r="H86">
         <v>5</v>
       </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="L86" t="s">
+      <c r="J86" t="s">
+        <v>35</v>
+      </c>
+      <c r="K86" t="s">
         <v>37</v>
       </c>
-      <c r="M86" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A87">
         <v>666</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C87">
         <v>5</v>
@@ -3841,25 +3424,19 @@
       <c r="H87">
         <v>5</v>
       </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="L87" t="s">
-        <v>37</v>
-      </c>
-      <c r="M87" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
+      <c r="J87" t="s">
+        <v>35</v>
+      </c>
+      <c r="K87" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A88">
         <v>973</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -3879,28 +3456,22 @@
       <c r="H88">
         <v>5</v>
       </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
+      <c r="I88" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" t="s">
+        <v>35</v>
       </c>
       <c r="K88" t="s">
-        <v>20</v>
-      </c>
-      <c r="L88" t="s">
-        <v>37</v>
-      </c>
-      <c r="M88" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A89">
         <v>565</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C89">
         <v>5</v>
@@ -3920,25 +3491,22 @@
       <c r="H89">
         <v>5</v>
       </c>
-      <c r="I89" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="L89" t="s">
-        <v>37</v>
-      </c>
-      <c r="M89" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="I89" t="s">
+        <v>39</v>
+      </c>
+      <c r="J89" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A90">
         <v>213</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C90">
         <v>5</v>
@@ -3958,25 +3526,19 @@
       <c r="H90">
         <v>5</v>
       </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="L90" t="s">
-        <v>37</v>
-      </c>
-      <c r="M90" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="J90" t="s">
+        <v>35</v>
+      </c>
+      <c r="K90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A91">
         <v>194</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C91">
         <v>5</v>
@@ -3996,25 +3558,19 @@
       <c r="H91">
         <v>5</v>
       </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" t="s">
+      <c r="J91" t="s">
+        <v>35</v>
+      </c>
+      <c r="K91" t="s">
         <v>37</v>
       </c>
-      <c r="M91" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A92">
         <v>479</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -4034,25 +3590,19 @@
       <c r="H92">
         <v>5</v>
       </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="L92" t="s">
-        <v>37</v>
-      </c>
-      <c r="M92" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="J92" t="s">
+        <v>35</v>
+      </c>
+      <c r="K92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A93">
         <v>696</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C93">
         <v>5</v>
@@ -4072,25 +3622,19 @@
       <c r="H93">
         <v>5</v>
       </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="L93" t="s">
-        <v>37</v>
-      </c>
-      <c r="M93" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="J93" t="s">
+        <v>35</v>
+      </c>
+      <c r="K93" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A94">
         <v>830</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C94">
         <v>5</v>
@@ -4110,28 +3654,22 @@
       <c r="H94">
         <v>5</v>
       </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
+      <c r="I94" t="s">
+        <v>27</v>
+      </c>
+      <c r="J94" t="s">
+        <v>35</v>
       </c>
       <c r="K94" t="s">
-        <v>29</v>
-      </c>
-      <c r="L94" t="s">
         <v>37</v>
       </c>
-      <c r="M94" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A95">
         <v>254</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -4151,25 +3689,19 @@
       <c r="H95">
         <v>4</v>
       </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="L95" t="s">
-        <v>37</v>
-      </c>
-      <c r="M95" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="J95" t="s">
+        <v>35</v>
+      </c>
+      <c r="K95" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A96">
         <v>908</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C96">
         <v>5</v>
@@ -4189,25 +3721,19 @@
       <c r="H96">
         <v>4</v>
       </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="J96" t="s">
+        <v>35</v>
+      </c>
+      <c r="K96" t="s">
         <v>37</v>
       </c>
-      <c r="M96" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A97">
         <v>597</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C97">
         <v>4</v>
@@ -4227,25 +3753,19 @@
       <c r="H97">
         <v>5</v>
       </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="L97" t="s">
-        <v>37</v>
-      </c>
-      <c r="M97" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13">
+      <c r="J97" t="s">
+        <v>35</v>
+      </c>
+      <c r="K97" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A98">
         <v>323</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C98">
         <v>4</v>
@@ -4265,25 +3785,19 @@
       <c r="H98">
         <v>5</v>
       </c>
-      <c r="I98" t="b">
-        <v>0</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="L98" t="s">
-        <v>37</v>
-      </c>
-      <c r="M98" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13">
+      <c r="J98" t="s">
+        <v>35</v>
+      </c>
+      <c r="K98" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A99">
         <v>469</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C99">
         <v>5</v>
@@ -4303,25 +3817,19 @@
       <c r="H99">
         <v>5</v>
       </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="L99" t="s">
-        <v>37</v>
-      </c>
-      <c r="M99" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13">
+      <c r="J99" t="s">
+        <v>35</v>
+      </c>
+      <c r="K99" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A100">
         <v>816</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C100">
         <v>5</v>
@@ -4341,25 +3849,19 @@
       <c r="H100">
         <v>5</v>
       </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="L100" t="s">
-        <v>37</v>
-      </c>
-      <c r="M100" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
+      <c r="J100" t="s">
+        <v>35</v>
+      </c>
+      <c r="K100" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A101">
         <v>944</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C101">
         <v>5</v>
@@ -4379,25 +3881,19 @@
       <c r="H101">
         <v>5</v>
       </c>
-      <c r="I101" t="b">
-        <v>0</v>
-      </c>
-      <c r="J101" t="b">
-        <v>0</v>
-      </c>
-      <c r="L101" t="s">
-        <v>37</v>
-      </c>
-      <c r="M101" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13">
+      <c r="J101" t="s">
+        <v>35</v>
+      </c>
+      <c r="K101" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A102">
         <v>471</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C102">
         <v>4</v>
@@ -4417,25 +3913,19 @@
       <c r="H102">
         <v>5</v>
       </c>
-      <c r="I102" t="b">
-        <v>0</v>
-      </c>
-      <c r="J102" t="b">
-        <v>0</v>
-      </c>
-      <c r="L102" t="s">
-        <v>37</v>
-      </c>
-      <c r="M102" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13">
+      <c r="J102" t="s">
+        <v>35</v>
+      </c>
+      <c r="K102" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A103">
         <v>607</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C103">
         <v>5</v>
@@ -4455,28 +3945,22 @@
       <c r="H103">
         <v>5</v>
       </c>
-      <c r="I103" t="b">
-        <v>0</v>
-      </c>
-      <c r="J103" t="b">
-        <v>0</v>
+      <c r="I103" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" t="s">
+        <v>35</v>
       </c>
       <c r="K103" t="s">
-        <v>26</v>
-      </c>
-      <c r="L103" t="s">
-        <v>37</v>
-      </c>
-      <c r="M103" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A104">
         <v>933</v>
       </c>
       <c r="B104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C104">
         <v>5</v>
@@ -4496,28 +3980,22 @@
       <c r="H104">
         <v>5</v>
       </c>
-      <c r="I104" t="b">
-        <v>0</v>
-      </c>
-      <c r="J104" t="b">
-        <v>0</v>
+      <c r="I104" t="s">
+        <v>20</v>
+      </c>
+      <c r="J104" t="s">
+        <v>35</v>
       </c>
       <c r="K104" t="s">
-        <v>22</v>
-      </c>
-      <c r="L104" t="s">
-        <v>37</v>
-      </c>
-      <c r="M104" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A105">
         <v>490</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C105">
         <v>5</v>
@@ -4537,28 +4015,22 @@
       <c r="H105">
         <v>5</v>
       </c>
-      <c r="I105" t="b">
-        <v>0</v>
-      </c>
-      <c r="J105" t="b">
-        <v>0</v>
+      <c r="I105" t="s">
+        <v>20</v>
+      </c>
+      <c r="J105" t="s">
+        <v>35</v>
       </c>
       <c r="K105" t="s">
-        <v>22</v>
-      </c>
-      <c r="L105" t="s">
         <v>37</v>
       </c>
-      <c r="M105" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A106">
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C106">
         <v>5</v>
@@ -4578,25 +4050,19 @@
       <c r="H106">
         <v>4</v>
       </c>
-      <c r="I106" t="b">
-        <v>0</v>
-      </c>
-      <c r="J106" t="b">
-        <v>0</v>
-      </c>
-      <c r="L106" t="s">
-        <v>37</v>
-      </c>
-      <c r="M106" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13">
+      <c r="J106" t="s">
+        <v>35</v>
+      </c>
+      <c r="K106" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A107">
         <v>44</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C107">
         <v>5</v>
@@ -4616,25 +4082,19 @@
       <c r="H107">
         <v>5</v>
       </c>
-      <c r="I107" t="b">
-        <v>0</v>
-      </c>
-      <c r="J107" t="b">
-        <v>0</v>
-      </c>
-      <c r="L107" t="s">
-        <v>37</v>
-      </c>
-      <c r="M107" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13">
+      <c r="J107" t="s">
+        <v>35</v>
+      </c>
+      <c r="K107" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A108">
         <v>855</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C108">
         <v>5</v>
@@ -4654,28 +4114,22 @@
       <c r="H108">
         <v>5</v>
       </c>
-      <c r="I108" t="b">
-        <v>0</v>
-      </c>
-      <c r="J108" t="b">
-        <v>0</v>
+      <c r="I108" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" t="s">
+        <v>35</v>
       </c>
       <c r="K108" t="s">
-        <v>28</v>
-      </c>
-      <c r="L108" t="s">
-        <v>37</v>
-      </c>
-      <c r="M108" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A109">
         <v>669</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -4695,25 +4149,19 @@
       <c r="H109">
         <v>5</v>
       </c>
-      <c r="I109" t="b">
-        <v>0</v>
-      </c>
-      <c r="J109" t="b">
-        <v>0</v>
-      </c>
-      <c r="L109" t="s">
-        <v>37</v>
-      </c>
-      <c r="M109" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13">
+      <c r="J109" t="s">
+        <v>35</v>
+      </c>
+      <c r="K109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A110">
         <v>897</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C110">
         <v>5</v>
@@ -4733,25 +4181,22 @@
       <c r="H110">
         <v>5</v>
       </c>
-      <c r="I110" t="b">
-        <v>0</v>
-      </c>
-      <c r="J110" t="b">
-        <v>0</v>
-      </c>
-      <c r="L110" t="s">
-        <v>37</v>
-      </c>
-      <c r="M110" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13">
+      <c r="I110" t="s">
+        <v>52</v>
+      </c>
+      <c r="J110" t="s">
+        <v>35</v>
+      </c>
+      <c r="K110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A111">
         <v>29</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C111">
         <v>5</v>
@@ -4771,25 +4216,19 @@
       <c r="H111">
         <v>4</v>
       </c>
-      <c r="I111" t="b">
-        <v>0</v>
-      </c>
-      <c r="J111" t="b">
-        <v>0</v>
-      </c>
-      <c r="L111" t="s">
+      <c r="J111" t="s">
+        <v>35</v>
+      </c>
+      <c r="K111" t="s">
         <v>37</v>
       </c>
-      <c r="M111" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A112">
         <v>646</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -4809,28 +4248,22 @@
       <c r="H112">
         <v>5</v>
       </c>
-      <c r="I112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J112" t="b">
-        <v>0</v>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>35</v>
       </c>
       <c r="K112" t="s">
-        <v>23</v>
-      </c>
-      <c r="L112" t="s">
         <v>37</v>
       </c>
-      <c r="M112" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13">
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A113">
         <v>890</v>
       </c>
       <c r="B113" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C113">
         <v>5</v>
@@ -4850,25 +4283,19 @@
       <c r="H113">
         <v>5</v>
       </c>
-      <c r="I113" t="b">
-        <v>0</v>
-      </c>
-      <c r="J113" t="b">
-        <v>0</v>
-      </c>
-      <c r="L113" t="s">
+      <c r="J113" t="s">
+        <v>35</v>
+      </c>
+      <c r="K113" t="s">
         <v>37</v>
       </c>
-      <c r="M113" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A114">
         <v>567</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C114">
         <v>5</v>
@@ -4888,25 +4315,19 @@
       <c r="H114">
         <v>5</v>
       </c>
-      <c r="I114" t="b">
-        <v>0</v>
-      </c>
-      <c r="J114" t="b">
-        <v>0</v>
-      </c>
-      <c r="L114" t="s">
+      <c r="J114" t="s">
+        <v>35</v>
+      </c>
+      <c r="K114" t="s">
         <v>37</v>
       </c>
-      <c r="M114" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13">
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A115">
         <v>739</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -4926,25 +4347,19 @@
       <c r="H115">
         <v>5</v>
       </c>
-      <c r="I115" t="b">
-        <v>0</v>
-      </c>
-      <c r="J115" t="b">
-        <v>0</v>
-      </c>
-      <c r="L115" t="s">
+      <c r="J115" t="s">
+        <v>35</v>
+      </c>
+      <c r="K115" t="s">
         <v>37</v>
       </c>
-      <c r="M115" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13">
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A116">
         <v>563</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C116">
         <v>5</v>
@@ -4964,28 +4379,22 @@
       <c r="H116">
         <v>4</v>
       </c>
-      <c r="I116" t="b">
-        <v>1</v>
-      </c>
-      <c r="J116" t="b">
-        <v>0</v>
+      <c r="I116" t="s">
+        <v>28</v>
+      </c>
+      <c r="J116" t="s">
+        <v>35</v>
       </c>
       <c r="K116" t="s">
-        <v>30</v>
-      </c>
-      <c r="L116" t="s">
-        <v>37</v>
-      </c>
-      <c r="M116" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A117">
         <v>537</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C117">
         <v>4</v>
@@ -5005,28 +4414,22 @@
       <c r="H117">
         <v>5</v>
       </c>
-      <c r="I117" t="b">
-        <v>0</v>
-      </c>
-      <c r="J117" t="b">
-        <v>0</v>
+      <c r="I117" t="s">
+        <v>24</v>
+      </c>
+      <c r="J117" t="s">
+        <v>35</v>
       </c>
       <c r="K117" t="s">
-        <v>26</v>
-      </c>
-      <c r="L117" t="s">
-        <v>37</v>
-      </c>
-      <c r="M117" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A118">
         <v>452</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C118">
         <v>5</v>
@@ -5046,25 +4449,19 @@
       <c r="H118">
         <v>5</v>
       </c>
-      <c r="I118" t="b">
-        <v>0</v>
-      </c>
-      <c r="J118" t="b">
-        <v>0</v>
-      </c>
-      <c r="L118" t="s">
-        <v>37</v>
-      </c>
-      <c r="M118" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13">
+      <c r="J118" t="s">
+        <v>35</v>
+      </c>
+      <c r="K118" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A119">
         <v>843</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C119">
         <v>5</v>
@@ -5084,25 +4481,19 @@
       <c r="H119">
         <v>5</v>
       </c>
-      <c r="I119" t="b">
-        <v>0</v>
-      </c>
-      <c r="J119" t="b">
-        <v>0</v>
-      </c>
-      <c r="L119" t="s">
-        <v>37</v>
-      </c>
-      <c r="M119" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13">
+      <c r="J119" t="s">
+        <v>35</v>
+      </c>
+      <c r="K119" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A120">
         <v>406</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C120">
         <v>5</v>
@@ -5122,25 +4513,19 @@
       <c r="H120">
         <v>5</v>
       </c>
-      <c r="I120" t="b">
-        <v>0</v>
-      </c>
-      <c r="J120" t="b">
-        <v>0</v>
-      </c>
-      <c r="L120" t="s">
-        <v>37</v>
-      </c>
-      <c r="M120" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13">
+      <c r="J120" t="s">
+        <v>35</v>
+      </c>
+      <c r="K120" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A121">
         <v>881</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C121">
         <v>5</v>
@@ -5160,25 +4545,19 @@
       <c r="H121">
         <v>5</v>
       </c>
-      <c r="I121" t="b">
-        <v>0</v>
-      </c>
-      <c r="J121" t="b">
-        <v>0</v>
-      </c>
-      <c r="L121" t="s">
+      <c r="J121" t="s">
+        <v>35</v>
+      </c>
+      <c r="K121" t="s">
         <v>37</v>
       </c>
-      <c r="M121" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13">
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A122">
         <v>612</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C122">
         <v>5</v>
@@ -5198,25 +4577,19 @@
       <c r="H122">
         <v>5</v>
       </c>
-      <c r="I122" t="b">
-        <v>0</v>
-      </c>
-      <c r="J122" t="b">
-        <v>0</v>
-      </c>
-      <c r="L122" t="s">
+      <c r="J122" t="s">
+        <v>35</v>
+      </c>
+      <c r="K122" t="s">
         <v>37</v>
       </c>
-      <c r="M122" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13">
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A123">
         <v>88</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C123">
         <v>5</v>
@@ -5236,25 +4609,19 @@
       <c r="H123">
         <v>5</v>
       </c>
-      <c r="I123" t="b">
-        <v>0</v>
-      </c>
-      <c r="J123" t="b">
-        <v>0</v>
-      </c>
-      <c r="L123" t="s">
-        <v>37</v>
-      </c>
-      <c r="M123" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13">
+      <c r="J123" t="s">
+        <v>35</v>
+      </c>
+      <c r="K123" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A124">
         <v>627</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C124">
         <v>5</v>
@@ -5274,25 +4641,19 @@
       <c r="H124">
         <v>5</v>
       </c>
-      <c r="I124" t="b">
-        <v>0</v>
-      </c>
-      <c r="J124" t="b">
-        <v>0</v>
-      </c>
-      <c r="L124" t="s">
+      <c r="J124" t="s">
+        <v>35</v>
+      </c>
+      <c r="K124" t="s">
         <v>37</v>
       </c>
-      <c r="M124" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13">
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A125">
         <v>486</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C125">
         <v>4</v>
@@ -5312,25 +4673,19 @@
       <c r="H125">
         <v>5</v>
       </c>
-      <c r="I125" t="b">
-        <v>0</v>
-      </c>
-      <c r="J125" t="b">
-        <v>0</v>
-      </c>
-      <c r="L125" t="s">
-        <v>37</v>
-      </c>
-      <c r="M125" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13">
+      <c r="J125" t="s">
+        <v>35</v>
+      </c>
+      <c r="K125" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A126">
         <v>716</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C126">
         <v>4</v>
@@ -5350,25 +4705,19 @@
       <c r="H126">
         <v>5</v>
       </c>
-      <c r="I126" t="b">
-        <v>0</v>
-      </c>
-      <c r="J126" t="b">
-        <v>0</v>
-      </c>
-      <c r="L126" t="s">
-        <v>37</v>
-      </c>
-      <c r="M126" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13">
+      <c r="J126" t="s">
+        <v>35</v>
+      </c>
+      <c r="K126" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A127">
         <v>846</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -5388,25 +4737,19 @@
       <c r="H127">
         <v>5</v>
       </c>
-      <c r="I127" t="b">
-        <v>0</v>
-      </c>
-      <c r="J127" t="b">
-        <v>0</v>
-      </c>
-      <c r="L127" t="s">
-        <v>37</v>
-      </c>
-      <c r="M127" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13">
+      <c r="J127" t="s">
+        <v>35</v>
+      </c>
+      <c r="K127" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A128">
         <v>905</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C128">
         <v>5</v>
@@ -5426,25 +4769,19 @@
       <c r="H128">
         <v>5</v>
       </c>
-      <c r="I128" t="b">
-        <v>0</v>
-      </c>
-      <c r="J128" t="b">
-        <v>0</v>
-      </c>
-      <c r="L128" t="s">
-        <v>37</v>
-      </c>
-      <c r="M128" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13">
+      <c r="J128" t="s">
+        <v>35</v>
+      </c>
+      <c r="K128" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A129">
         <v>391</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C129">
         <v>5</v>
@@ -5464,25 +4801,19 @@
       <c r="H129">
         <v>5</v>
       </c>
-      <c r="I129" t="b">
-        <v>0</v>
-      </c>
-      <c r="J129" t="b">
-        <v>0</v>
-      </c>
-      <c r="L129" t="s">
-        <v>37</v>
-      </c>
-      <c r="M129" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13">
+      <c r="J129" t="s">
+        <v>35</v>
+      </c>
+      <c r="K129" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A130">
         <v>322</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C130">
         <v>5</v>
@@ -5502,25 +4833,19 @@
       <c r="H130">
         <v>5</v>
       </c>
-      <c r="I130" t="b">
-        <v>0</v>
-      </c>
-      <c r="J130" t="b">
-        <v>0</v>
-      </c>
-      <c r="L130" t="s">
-        <v>37</v>
-      </c>
-      <c r="M130" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13">
+      <c r="J130" t="s">
+        <v>35</v>
+      </c>
+      <c r="K130" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A131">
         <v>750</v>
       </c>
       <c r="B131" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C131">
         <v>5</v>
@@ -5540,25 +4865,19 @@
       <c r="H131">
         <v>4</v>
       </c>
-      <c r="I131" t="b">
-        <v>0</v>
-      </c>
-      <c r="J131" t="b">
-        <v>0</v>
-      </c>
-      <c r="L131" t="s">
-        <v>37</v>
-      </c>
-      <c r="M131" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13">
+      <c r="J131" t="s">
+        <v>35</v>
+      </c>
+      <c r="K131" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A132">
         <v>961</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C132">
         <v>4</v>
@@ -5578,25 +4897,19 @@
       <c r="H132">
         <v>5</v>
       </c>
-      <c r="I132" t="b">
-        <v>0</v>
-      </c>
-      <c r="J132" t="b">
-        <v>0</v>
-      </c>
-      <c r="L132" t="s">
-        <v>37</v>
-      </c>
-      <c r="M132" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13">
+      <c r="J132" t="s">
+        <v>35</v>
+      </c>
+      <c r="K132" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A133">
         <v>457</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -5616,28 +4929,22 @@
       <c r="H133">
         <v>5</v>
       </c>
-      <c r="I133" t="b">
-        <v>1</v>
-      </c>
-      <c r="J133" t="b">
-        <v>0</v>
+      <c r="I133" t="s">
+        <v>29</v>
+      </c>
+      <c r="J133" t="s">
+        <v>35</v>
       </c>
       <c r="K133" t="s">
-        <v>31</v>
-      </c>
-      <c r="L133" t="s">
         <v>37</v>
       </c>
-      <c r="M133" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13">
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A134">
         <v>938</v>
       </c>
       <c r="B134" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C134">
         <v>4</v>
@@ -5657,25 +4964,22 @@
       <c r="H134">
         <v>4</v>
       </c>
-      <c r="I134" t="b">
-        <v>1</v>
-      </c>
-      <c r="J134" t="b">
-        <v>0</v>
-      </c>
-      <c r="L134" t="s">
-        <v>37</v>
-      </c>
-      <c r="M134" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13">
+      <c r="I134" t="s">
+        <v>39</v>
+      </c>
+      <c r="J134" t="s">
+        <v>35</v>
+      </c>
+      <c r="K134" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A135">
         <v>779</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C135">
         <v>4</v>
@@ -5695,25 +4999,19 @@
       <c r="H135">
         <v>4</v>
       </c>
-      <c r="I135" t="b">
-        <v>0</v>
-      </c>
-      <c r="J135" t="b">
-        <v>0</v>
-      </c>
-      <c r="L135" t="s">
-        <v>37</v>
-      </c>
-      <c r="M135" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13">
+      <c r="J135" t="s">
+        <v>35</v>
+      </c>
+      <c r="K135" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A136">
         <v>657</v>
       </c>
       <c r="B136" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C136">
         <v>5</v>
@@ -5733,28 +5031,22 @@
       <c r="H136">
         <v>5</v>
       </c>
-      <c r="I136" t="b">
-        <v>1</v>
-      </c>
-      <c r="J136" t="b">
-        <v>0</v>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" t="s">
+        <v>35</v>
       </c>
       <c r="K136" t="s">
-        <v>20</v>
-      </c>
-      <c r="L136" t="s">
         <v>37</v>
       </c>
-      <c r="M136" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13">
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A137">
         <v>331</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C137">
         <v>5</v>
@@ -5774,25 +5066,19 @@
       <c r="H137">
         <v>5</v>
       </c>
-      <c r="I137" t="b">
-        <v>0</v>
-      </c>
-      <c r="J137" t="b">
-        <v>0</v>
-      </c>
-      <c r="L137" t="s">
-        <v>37</v>
-      </c>
-      <c r="M137" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13">
+      <c r="J137" t="s">
+        <v>35</v>
+      </c>
+      <c r="K137" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A138">
         <v>546</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C138">
         <v>4</v>
@@ -5812,25 +5098,19 @@
       <c r="H138">
         <v>5</v>
       </c>
-      <c r="I138" t="b">
-        <v>0</v>
-      </c>
-      <c r="J138" t="b">
-        <v>0</v>
-      </c>
-      <c r="L138" t="s">
-        <v>37</v>
-      </c>
-      <c r="M138" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13">
+      <c r="J138" t="s">
+        <v>35</v>
+      </c>
+      <c r="K138" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A139">
         <v>794</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C139">
         <v>5</v>
@@ -5850,25 +5130,19 @@
       <c r="H139">
         <v>5</v>
       </c>
-      <c r="I139" t="b">
-        <v>0</v>
-      </c>
-      <c r="J139" t="b">
-        <v>0</v>
-      </c>
-      <c r="L139" t="s">
-        <v>37</v>
-      </c>
-      <c r="M139" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13">
+      <c r="J139" t="s">
+        <v>35</v>
+      </c>
+      <c r="K139" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A140">
         <v>730</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C140">
         <v>5</v>
@@ -5888,25 +5162,19 @@
       <c r="H140">
         <v>5</v>
       </c>
-      <c r="I140" t="b">
-        <v>0</v>
-      </c>
-      <c r="J140" t="b">
-        <v>0</v>
-      </c>
-      <c r="L140" t="s">
-        <v>37</v>
-      </c>
-      <c r="M140" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13">
+      <c r="J140" t="s">
+        <v>35</v>
+      </c>
+      <c r="K140" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A141">
         <v>934</v>
       </c>
       <c r="B141" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C141">
         <v>5</v>
@@ -5926,25 +5194,22 @@
       <c r="H141">
         <v>5</v>
       </c>
-      <c r="I141" t="b">
-        <v>1</v>
-      </c>
-      <c r="J141" t="b">
-        <v>0</v>
-      </c>
-      <c r="L141" t="s">
-        <v>37</v>
-      </c>
-      <c r="M141" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13">
+      <c r="I141" t="s">
+        <v>53</v>
+      </c>
+      <c r="J141" t="s">
+        <v>35</v>
+      </c>
+      <c r="K141" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A142">
         <v>584</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C142">
         <v>5</v>
@@ -5964,28 +5229,22 @@
       <c r="H142">
         <v>5</v>
       </c>
-      <c r="I142" t="b">
-        <v>0</v>
-      </c>
-      <c r="J142" t="b">
-        <v>0</v>
+      <c r="I142" t="s">
+        <v>30</v>
+      </c>
+      <c r="J142" t="s">
+        <v>35</v>
       </c>
       <c r="K142" t="s">
-        <v>32</v>
-      </c>
-      <c r="L142" t="s">
         <v>37</v>
       </c>
-      <c r="M142" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13">
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A143">
         <v>167</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C143">
         <v>5</v>
@@ -6005,25 +5264,19 @@
       <c r="H143">
         <v>5</v>
       </c>
-      <c r="I143" t="b">
-        <v>0</v>
-      </c>
-      <c r="J143" t="b">
-        <v>0</v>
-      </c>
-      <c r="L143" t="s">
-        <v>37</v>
-      </c>
-      <c r="M143" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13">
+      <c r="J143" t="s">
+        <v>35</v>
+      </c>
+      <c r="K143" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A144">
         <v>385</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C144">
         <v>5</v>
@@ -6043,25 +5296,19 @@
       <c r="H144">
         <v>4</v>
       </c>
-      <c r="I144" t="b">
-        <v>0</v>
-      </c>
-      <c r="J144" t="b">
-        <v>0</v>
-      </c>
-      <c r="L144" t="s">
-        <v>37</v>
-      </c>
-      <c r="M144" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13">
+      <c r="J144" t="s">
+        <v>35</v>
+      </c>
+      <c r="K144" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A145">
         <v>270</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C145">
         <v>5</v>
@@ -6081,28 +5328,22 @@
       <c r="H145">
         <v>5</v>
       </c>
-      <c r="I145" t="b">
-        <v>1</v>
-      </c>
-      <c r="J145" t="b">
-        <v>0</v>
+      <c r="I145" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" t="s">
+        <v>35</v>
       </c>
       <c r="K145" t="s">
-        <v>19</v>
-      </c>
-      <c r="L145" t="s">
         <v>37</v>
       </c>
-      <c r="M145" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13">
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A146">
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C146">
         <v>5</v>
@@ -6122,25 +5363,19 @@
       <c r="H146">
         <v>5</v>
       </c>
-      <c r="I146" t="b">
-        <v>0</v>
-      </c>
-      <c r="J146" t="b">
-        <v>0</v>
-      </c>
-      <c r="L146" t="s">
-        <v>37</v>
-      </c>
-      <c r="M146" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13">
+      <c r="J146" t="s">
+        <v>35</v>
+      </c>
+      <c r="K146" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A147">
         <v>137</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C147">
         <v>5</v>
@@ -6160,25 +5395,19 @@
       <c r="H147">
         <v>4</v>
       </c>
-      <c r="I147" t="b">
-        <v>0</v>
-      </c>
-      <c r="J147" t="b">
-        <v>0</v>
-      </c>
-      <c r="L147" t="s">
+      <c r="J147" t="s">
+        <v>35</v>
+      </c>
+      <c r="K147" t="s">
         <v>37</v>
       </c>
-      <c r="M147" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13">
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A148">
         <v>417</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C148">
         <v>5</v>
@@ -6198,25 +5427,19 @@
       <c r="H148">
         <v>5</v>
       </c>
-      <c r="I148" t="b">
-        <v>0</v>
-      </c>
-      <c r="J148" t="b">
-        <v>0</v>
-      </c>
-      <c r="L148" t="s">
-        <v>37</v>
-      </c>
-      <c r="M148" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13">
+      <c r="J148" t="s">
+        <v>35</v>
+      </c>
+      <c r="K148" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A149">
         <v>782</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C149">
         <v>4</v>
@@ -6236,25 +5459,19 @@
       <c r="H149">
         <v>5</v>
       </c>
-      <c r="I149" t="b">
-        <v>0</v>
-      </c>
-      <c r="J149" t="b">
-        <v>0</v>
-      </c>
-      <c r="L149" t="s">
-        <v>37</v>
-      </c>
-      <c r="M149" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13">
+      <c r="J149" t="s">
+        <v>35</v>
+      </c>
+      <c r="K149" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A150">
         <v>848</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C150">
         <v>5</v>
@@ -6274,25 +5491,19 @@
       <c r="H150">
         <v>5</v>
       </c>
-      <c r="I150" t="b">
-        <v>0</v>
-      </c>
-      <c r="J150" t="b">
-        <v>0</v>
-      </c>
-      <c r="L150" t="s">
-        <v>37</v>
-      </c>
-      <c r="M150" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13">
+      <c r="J150" t="s">
+        <v>35</v>
+      </c>
+      <c r="K150" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A151">
         <v>715</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C151">
         <v>5</v>
@@ -6312,28 +5523,22 @@
       <c r="H151">
         <v>4</v>
       </c>
-      <c r="I151" t="b">
-        <v>0</v>
-      </c>
-      <c r="J151" t="b">
-        <v>0</v>
+      <c r="I151" t="s">
+        <v>27</v>
+      </c>
+      <c r="J151" t="s">
+        <v>35</v>
       </c>
       <c r="K151" t="s">
-        <v>29</v>
-      </c>
-      <c r="L151" t="s">
-        <v>37</v>
-      </c>
-      <c r="M151" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A152">
         <v>569</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C152">
         <v>5</v>
@@ -6353,28 +5558,22 @@
       <c r="H152">
         <v>5</v>
       </c>
-      <c r="I152" t="b">
-        <v>0</v>
-      </c>
-      <c r="J152" t="b">
-        <v>0</v>
+      <c r="I152" t="s">
+        <v>15</v>
+      </c>
+      <c r="J152" t="s">
+        <v>35</v>
       </c>
       <c r="K152" t="s">
-        <v>17</v>
-      </c>
-      <c r="L152" t="s">
-        <v>37</v>
-      </c>
-      <c r="M152" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A153">
         <v>73</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C153">
         <v>5</v>
@@ -6394,28 +5593,22 @@
       <c r="H153">
         <v>5</v>
       </c>
-      <c r="I153" t="b">
-        <v>1</v>
-      </c>
-      <c r="J153" t="b">
-        <v>1</v>
+      <c r="I153" t="s">
+        <v>31</v>
+      </c>
+      <c r="J153" t="s">
+        <v>35</v>
       </c>
       <c r="K153" t="s">
-        <v>33</v>
-      </c>
-      <c r="L153" t="s">
         <v>37</v>
       </c>
-      <c r="M153" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A154">
         <v>264</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C154">
         <v>5</v>
@@ -6435,25 +5628,19 @@
       <c r="H154">
         <v>5</v>
       </c>
-      <c r="I154" t="b">
-        <v>0</v>
-      </c>
-      <c r="J154" t="b">
-        <v>0</v>
-      </c>
-      <c r="L154" t="s">
-        <v>37</v>
-      </c>
-      <c r="M154" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13">
+      <c r="J154" t="s">
+        <v>35</v>
+      </c>
+      <c r="K154" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A155">
         <v>690</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C155">
         <v>5</v>
@@ -6473,25 +5660,19 @@
       <c r="H155">
         <v>5</v>
       </c>
-      <c r="I155" t="b">
-        <v>0</v>
-      </c>
-      <c r="J155" t="b">
-        <v>0</v>
-      </c>
-      <c r="L155" t="s">
-        <v>37</v>
-      </c>
-      <c r="M155" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13">
+      <c r="J155" t="s">
+        <v>35</v>
+      </c>
+      <c r="K155" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A156">
         <v>629</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C156">
         <v>5</v>
@@ -6511,28 +5692,22 @@
       <c r="H156">
         <v>5</v>
       </c>
-      <c r="I156" t="b">
-        <v>0</v>
-      </c>
-      <c r="J156" t="b">
-        <v>0</v>
+      <c r="I156" t="s">
+        <v>15</v>
+      </c>
+      <c r="J156" t="s">
+        <v>35</v>
       </c>
       <c r="K156" t="s">
-        <v>17</v>
-      </c>
-      <c r="L156" t="s">
-        <v>37</v>
-      </c>
-      <c r="M156" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A157">
         <v>589</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C157">
         <v>4</v>
@@ -6552,25 +5727,19 @@
       <c r="H157">
         <v>5</v>
       </c>
-      <c r="I157" t="b">
-        <v>1</v>
-      </c>
-      <c r="J157" t="b">
-        <v>0</v>
-      </c>
-      <c r="L157" t="s">
-        <v>37</v>
-      </c>
-      <c r="M157" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13">
+      <c r="J157" t="s">
+        <v>35</v>
+      </c>
+      <c r="K157" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A158">
         <v>498</v>
       </c>
       <c r="B158" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C158">
         <v>5</v>
@@ -6590,25 +5759,19 @@
       <c r="H158">
         <v>5</v>
       </c>
-      <c r="I158" t="b">
-        <v>0</v>
-      </c>
-      <c r="J158" t="b">
-        <v>0</v>
-      </c>
-      <c r="L158" t="s">
+      <c r="J158" t="s">
+        <v>35</v>
+      </c>
+      <c r="K158" t="s">
         <v>37</v>
       </c>
-      <c r="M158" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13">
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A159">
         <v>244</v>
       </c>
       <c r="B159" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C159">
         <v>5</v>
@@ -6628,25 +5791,19 @@
       <c r="H159">
         <v>5</v>
       </c>
-      <c r="I159" t="b">
-        <v>0</v>
-      </c>
-      <c r="J159" t="b">
-        <v>0</v>
-      </c>
-      <c r="L159" t="s">
-        <v>37</v>
-      </c>
-      <c r="M159" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13">
+      <c r="J159" t="s">
+        <v>35</v>
+      </c>
+      <c r="K159" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A160">
         <v>72</v>
       </c>
       <c r="B160" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C160">
         <v>5</v>
@@ -6666,25 +5823,22 @@
       <c r="H160">
         <v>5</v>
       </c>
-      <c r="I160" t="b">
-        <v>1</v>
-      </c>
-      <c r="J160" t="b">
-        <v>1</v>
-      </c>
-      <c r="L160" t="s">
+      <c r="I160" t="s">
+        <v>40</v>
+      </c>
+      <c r="J160" t="s">
+        <v>35</v>
+      </c>
+      <c r="K160" t="s">
         <v>37</v>
       </c>
-      <c r="M160" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13">
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A161">
         <v>814</v>
       </c>
       <c r="B161" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C161">
         <v>5</v>
@@ -6704,25 +5858,19 @@
       <c r="H161">
         <v>5</v>
       </c>
-      <c r="I161" t="b">
-        <v>0</v>
-      </c>
-      <c r="J161" t="b">
-        <v>0</v>
-      </c>
-      <c r="L161" t="s">
-        <v>37</v>
-      </c>
-      <c r="M161" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13">
+      <c r="J161" t="s">
+        <v>35</v>
+      </c>
+      <c r="K161" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A162">
         <v>718</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C162">
         <v>5</v>
@@ -6742,25 +5890,19 @@
       <c r="H162">
         <v>5</v>
       </c>
-      <c r="I162" t="b">
-        <v>0</v>
-      </c>
-      <c r="J162" t="b">
-        <v>0</v>
-      </c>
-      <c r="L162" t="s">
+      <c r="J162" t="s">
+        <v>35</v>
+      </c>
+      <c r="K162" t="s">
         <v>37</v>
       </c>
-      <c r="M162" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13">
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A163">
         <v>753</v>
       </c>
       <c r="B163" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C163">
         <v>5</v>
@@ -6780,25 +5922,19 @@
       <c r="H163">
         <v>5</v>
       </c>
-      <c r="I163" t="b">
-        <v>0</v>
-      </c>
-      <c r="J163" t="b">
-        <v>0</v>
-      </c>
-      <c r="L163" t="s">
+      <c r="J163" t="s">
+        <v>35</v>
+      </c>
+      <c r="K163" t="s">
         <v>37</v>
       </c>
-      <c r="M163" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13">
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A164">
         <v>357</v>
       </c>
       <c r="B164" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C164">
         <v>5</v>
@@ -6818,25 +5954,22 @@
       <c r="H164">
         <v>4</v>
       </c>
-      <c r="I164" t="b">
-        <v>1</v>
-      </c>
-      <c r="J164" t="b">
-        <v>0</v>
-      </c>
-      <c r="L164" t="s">
-        <v>37</v>
-      </c>
-      <c r="M164" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13">
+      <c r="I164" t="s">
+        <v>41</v>
+      </c>
+      <c r="J164" t="s">
+        <v>35</v>
+      </c>
+      <c r="K164" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A165">
         <v>581</v>
       </c>
       <c r="B165" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C165">
         <v>5</v>
@@ -6856,28 +5989,22 @@
       <c r="H165">
         <v>5</v>
       </c>
-      <c r="I165" t="b">
-        <v>1</v>
-      </c>
-      <c r="J165" t="b">
-        <v>0</v>
+      <c r="I165" t="s">
+        <v>32</v>
+      </c>
+      <c r="J165" t="s">
+        <v>35</v>
       </c>
       <c r="K165" t="s">
-        <v>34</v>
-      </c>
-      <c r="L165" t="s">
-        <v>37</v>
-      </c>
-      <c r="M165" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A166">
         <v>402</v>
       </c>
       <c r="B166" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C166">
         <v>5</v>
@@ -6897,25 +6024,19 @@
       <c r="H166">
         <v>4</v>
       </c>
-      <c r="I166" t="b">
-        <v>0</v>
-      </c>
-      <c r="J166" t="b">
-        <v>0</v>
-      </c>
-      <c r="L166" t="s">
-        <v>37</v>
-      </c>
-      <c r="M166" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13">
+      <c r="J166" t="s">
+        <v>35</v>
+      </c>
+      <c r="K166" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A167">
         <v>506</v>
       </c>
       <c r="B167" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -6935,25 +6056,19 @@
       <c r="H167">
         <v>4</v>
       </c>
-      <c r="I167" t="b">
-        <v>0</v>
-      </c>
-      <c r="J167" t="b">
-        <v>0</v>
-      </c>
-      <c r="L167" t="s">
-        <v>37</v>
-      </c>
-      <c r="M167" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="168" spans="1:13">
+      <c r="J167" t="s">
+        <v>35</v>
+      </c>
+      <c r="K167" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A168">
         <v>267</v>
       </c>
       <c r="B168" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C168">
         <v>5</v>
@@ -6973,28 +6088,22 @@
       <c r="H168">
         <v>5</v>
       </c>
-      <c r="I168" t="b">
-        <v>0</v>
-      </c>
-      <c r="J168" t="b">
-        <v>0</v>
+      <c r="I168" t="s">
+        <v>30</v>
+      </c>
+      <c r="J168" t="s">
+        <v>35</v>
       </c>
       <c r="K168" t="s">
-        <v>32</v>
-      </c>
-      <c r="L168" t="s">
         <v>37</v>
       </c>
-      <c r="M168" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13">
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A169">
         <v>328</v>
       </c>
       <c r="B169" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C169">
         <v>5</v>
@@ -7014,25 +6123,19 @@
       <c r="H169">
         <v>5</v>
       </c>
-      <c r="I169" t="b">
-        <v>0</v>
-      </c>
-      <c r="J169" t="b">
-        <v>0</v>
-      </c>
-      <c r="L169" t="s">
-        <v>37</v>
-      </c>
-      <c r="M169" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13">
+      <c r="J169" t="s">
+        <v>35</v>
+      </c>
+      <c r="K169" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A170">
         <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C170">
         <v>4</v>
@@ -7052,25 +6155,19 @@
       <c r="H170">
         <v>5</v>
       </c>
-      <c r="I170" t="b">
-        <v>0</v>
-      </c>
-      <c r="J170" t="b">
-        <v>0</v>
-      </c>
-      <c r="L170" t="s">
+      <c r="J170" t="s">
+        <v>35</v>
+      </c>
+      <c r="K170" t="s">
         <v>37</v>
       </c>
-      <c r="M170" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13">
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A171">
         <v>516</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C171">
         <v>5</v>
@@ -7090,25 +6187,19 @@
       <c r="H171">
         <v>5</v>
       </c>
-      <c r="I171" t="b">
-        <v>0</v>
-      </c>
-      <c r="J171" t="b">
-        <v>0</v>
-      </c>
-      <c r="L171" t="s">
-        <v>37</v>
-      </c>
-      <c r="M171" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13">
+      <c r="J171" t="s">
+        <v>35</v>
+      </c>
+      <c r="K171" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A172">
         <v>253</v>
       </c>
       <c r="B172" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C172">
         <v>5</v>
@@ -7128,25 +6219,22 @@
       <c r="H172">
         <v>5</v>
       </c>
-      <c r="I172" t="b">
-        <v>1</v>
-      </c>
-      <c r="J172" t="b">
-        <v>0</v>
-      </c>
-      <c r="L172" t="s">
-        <v>37</v>
-      </c>
-      <c r="M172" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13">
+      <c r="I172" t="s">
+        <v>54</v>
+      </c>
+      <c r="J172" t="s">
+        <v>35</v>
+      </c>
+      <c r="K172" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A173">
         <v>78</v>
       </c>
       <c r="B173" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C173">
         <v>5</v>
@@ -7166,28 +6254,22 @@
       <c r="H173">
         <v>5</v>
       </c>
-      <c r="I173" t="b">
-        <v>0</v>
-      </c>
-      <c r="J173" t="b">
-        <v>0</v>
+      <c r="I173" t="s">
+        <v>19</v>
+      </c>
+      <c r="J173" t="s">
+        <v>35</v>
       </c>
       <c r="K173" t="s">
-        <v>21</v>
-      </c>
-      <c r="L173" t="s">
-        <v>37</v>
-      </c>
-      <c r="M173" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="174" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A174">
         <v>349</v>
       </c>
       <c r="B174" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C174">
         <v>5</v>
@@ -7207,25 +6289,19 @@
       <c r="H174">
         <v>5</v>
       </c>
-      <c r="I174" t="b">
-        <v>0</v>
-      </c>
-      <c r="J174" t="b">
-        <v>0</v>
-      </c>
-      <c r="L174" t="s">
-        <v>37</v>
-      </c>
-      <c r="M174" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13">
+      <c r="J174" t="s">
+        <v>35</v>
+      </c>
+      <c r="K174" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A175">
         <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C175">
         <v>5</v>
@@ -7245,28 +6321,22 @@
       <c r="H175">
         <v>5</v>
       </c>
-      <c r="I175" t="b">
-        <v>0</v>
-      </c>
-      <c r="J175" t="b">
-        <v>0</v>
+      <c r="I175" t="s">
+        <v>26</v>
+      </c>
+      <c r="J175" t="s">
+        <v>35</v>
       </c>
       <c r="K175" t="s">
-        <v>28</v>
-      </c>
-      <c r="L175" t="s">
-        <v>37</v>
-      </c>
-      <c r="M175" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="176" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A176">
         <v>549</v>
       </c>
       <c r="B176" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C176">
         <v>5</v>
@@ -7286,28 +6356,22 @@
       <c r="H176">
         <v>5</v>
       </c>
-      <c r="I176" t="b">
-        <v>0</v>
-      </c>
-      <c r="J176" t="b">
-        <v>0</v>
+      <c r="I176" t="s">
+        <v>19</v>
+      </c>
+      <c r="J176" t="s">
+        <v>35</v>
       </c>
       <c r="K176" t="s">
-        <v>21</v>
-      </c>
-      <c r="L176" t="s">
         <v>37</v>
       </c>
-      <c r="M176" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13">
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A177">
         <v>265</v>
       </c>
       <c r="B177" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C177">
         <v>5</v>
@@ -7327,25 +6391,19 @@
       <c r="H177">
         <v>4</v>
       </c>
-      <c r="I177" t="b">
-        <v>0</v>
-      </c>
-      <c r="J177" t="b">
-        <v>0</v>
-      </c>
-      <c r="L177" t="s">
-        <v>37</v>
-      </c>
-      <c r="M177" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13">
+      <c r="J177" t="s">
+        <v>35</v>
+      </c>
+      <c r="K177" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A178">
         <v>153</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -7365,25 +6423,22 @@
       <c r="H178">
         <v>4</v>
       </c>
-      <c r="I178" t="b">
-        <v>1</v>
-      </c>
-      <c r="J178" t="b">
-        <v>0</v>
-      </c>
-      <c r="L178" t="s">
-        <v>37</v>
-      </c>
-      <c r="M178" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13">
+      <c r="I178" t="s">
+        <v>42</v>
+      </c>
+      <c r="J178" t="s">
+        <v>35</v>
+      </c>
+      <c r="K178" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A179">
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C179">
         <v>5</v>
@@ -7403,25 +6458,19 @@
       <c r="H179">
         <v>5</v>
       </c>
-      <c r="I179" t="b">
-        <v>0</v>
-      </c>
-      <c r="J179" t="b">
-        <v>0</v>
-      </c>
-      <c r="L179" t="s">
-        <v>37</v>
-      </c>
-      <c r="M179" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13">
+      <c r="J179" t="s">
+        <v>35</v>
+      </c>
+      <c r="K179" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A180">
         <v>558</v>
       </c>
       <c r="B180" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C180">
         <v>4</v>
@@ -7441,25 +6490,19 @@
       <c r="H180">
         <v>5</v>
       </c>
-      <c r="I180" t="b">
-        <v>0</v>
-      </c>
-      <c r="J180" t="b">
-        <v>0</v>
-      </c>
-      <c r="L180" t="s">
-        <v>37</v>
-      </c>
-      <c r="M180" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13">
+      <c r="J180" t="s">
+        <v>35</v>
+      </c>
+      <c r="K180" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A181">
         <v>318</v>
       </c>
       <c r="B181" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C181">
         <v>5</v>
@@ -7479,25 +6522,19 @@
       <c r="H181">
         <v>5</v>
       </c>
-      <c r="I181" t="b">
-        <v>0</v>
-      </c>
-      <c r="J181" t="b">
-        <v>0</v>
-      </c>
-      <c r="L181" t="s">
-        <v>37</v>
-      </c>
-      <c r="M181" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13">
+      <c r="J181" t="s">
+        <v>35</v>
+      </c>
+      <c r="K181" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A182">
         <v>761</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C182">
         <v>5</v>
@@ -7517,25 +6554,19 @@
       <c r="H182">
         <v>5</v>
       </c>
-      <c r="I182" t="b">
-        <v>0</v>
-      </c>
-      <c r="J182" t="b">
-        <v>0</v>
-      </c>
-      <c r="L182" t="s">
-        <v>37</v>
-      </c>
-      <c r="M182" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13">
+      <c r="J182" t="s">
+        <v>35</v>
+      </c>
+      <c r="K182" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A183">
         <v>131</v>
       </c>
       <c r="B183" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C183">
         <v>4</v>
@@ -7555,25 +6586,19 @@
       <c r="H183">
         <v>5</v>
       </c>
-      <c r="I183" t="b">
-        <v>0</v>
-      </c>
-      <c r="J183" t="b">
-        <v>0</v>
-      </c>
-      <c r="L183" t="s">
-        <v>37</v>
-      </c>
-      <c r="M183" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13">
+      <c r="J183" t="s">
+        <v>35</v>
+      </c>
+      <c r="K183" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A184">
         <v>150</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C184">
         <v>5</v>
@@ -7593,28 +6618,22 @@
       <c r="H184">
         <v>4</v>
       </c>
-      <c r="I184" t="b">
-        <v>0</v>
-      </c>
-      <c r="J184" t="b">
-        <v>0</v>
+      <c r="I184" t="s">
+        <v>27</v>
+      </c>
+      <c r="J184" t="s">
+        <v>35</v>
       </c>
       <c r="K184" t="s">
-        <v>29</v>
-      </c>
-      <c r="L184" t="s">
         <v>37</v>
       </c>
-      <c r="M184" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13">
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A185">
         <v>962</v>
       </c>
       <c r="B185" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C185">
         <v>5</v>
@@ -7634,25 +6653,19 @@
       <c r="H185">
         <v>5</v>
       </c>
-      <c r="I185" t="b">
-        <v>0</v>
-      </c>
-      <c r="J185" t="b">
-        <v>0</v>
-      </c>
-      <c r="L185" t="s">
-        <v>37</v>
-      </c>
-      <c r="M185" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13">
+      <c r="J185" t="s">
+        <v>35</v>
+      </c>
+      <c r="K185" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A186">
         <v>399</v>
       </c>
       <c r="B186" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C186">
         <v>5</v>
@@ -7672,25 +6685,19 @@
       <c r="H186">
         <v>5</v>
       </c>
-      <c r="I186" t="b">
-        <v>0</v>
-      </c>
-      <c r="J186" t="b">
-        <v>0</v>
-      </c>
-      <c r="L186" t="s">
-        <v>37</v>
-      </c>
-      <c r="M186" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13">
+      <c r="J186" t="s">
+        <v>35</v>
+      </c>
+      <c r="K186" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A187">
         <v>333</v>
       </c>
       <c r="B187" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C187">
         <v>5</v>
@@ -7710,25 +6717,19 @@
       <c r="H187">
         <v>4</v>
       </c>
-      <c r="I187" t="b">
-        <v>0</v>
-      </c>
-      <c r="J187" t="b">
-        <v>0</v>
-      </c>
-      <c r="L187" t="s">
-        <v>37</v>
-      </c>
-      <c r="M187" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13">
+      <c r="J187" t="s">
+        <v>35</v>
+      </c>
+      <c r="K187" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A188">
         <v>463</v>
       </c>
       <c r="B188" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C188">
         <v>4</v>
@@ -7748,25 +6749,19 @@
       <c r="H188">
         <v>4</v>
       </c>
-      <c r="I188" t="b">
-        <v>0</v>
-      </c>
-      <c r="J188" t="b">
-        <v>0</v>
-      </c>
-      <c r="L188" t="s">
-        <v>37</v>
-      </c>
-      <c r="M188" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13">
+      <c r="J188" t="s">
+        <v>35</v>
+      </c>
+      <c r="K188" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A189">
         <v>451</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C189">
         <v>5</v>
@@ -7786,25 +6781,19 @@
       <c r="H189">
         <v>5</v>
       </c>
-      <c r="I189" t="b">
-        <v>0</v>
-      </c>
-      <c r="J189" t="b">
-        <v>0</v>
-      </c>
-      <c r="L189" t="s">
-        <v>37</v>
-      </c>
-      <c r="M189" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13">
+      <c r="J189" t="s">
+        <v>35</v>
+      </c>
+      <c r="K189" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A190">
         <v>729</v>
       </c>
       <c r="B190" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C190">
         <v>5</v>
@@ -7824,28 +6813,22 @@
       <c r="H190">
         <v>5</v>
       </c>
-      <c r="I190" t="b">
-        <v>0</v>
-      </c>
-      <c r="J190" t="b">
-        <v>0</v>
+      <c r="I190" t="s">
+        <v>27</v>
+      </c>
+      <c r="J190" t="s">
+        <v>35</v>
       </c>
       <c r="K190" t="s">
-        <v>29</v>
-      </c>
-      <c r="L190" t="s">
-        <v>37</v>
-      </c>
-      <c r="M190" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A191">
         <v>304</v>
       </c>
       <c r="B191" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C191">
         <v>4</v>
@@ -7865,25 +6848,19 @@
       <c r="H191">
         <v>5</v>
       </c>
-      <c r="I191" t="b">
-        <v>0</v>
-      </c>
-      <c r="J191" t="b">
-        <v>0</v>
-      </c>
-      <c r="L191" t="s">
+      <c r="J191" t="s">
+        <v>35</v>
+      </c>
+      <c r="K191" t="s">
         <v>37</v>
       </c>
-      <c r="M191" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13">
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A192">
         <v>478</v>
       </c>
       <c r="B192" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C192">
         <v>5</v>
@@ -7903,28 +6880,22 @@
       <c r="H192">
         <v>5</v>
       </c>
-      <c r="I192" t="b">
-        <v>0</v>
-      </c>
-      <c r="J192" t="b">
-        <v>0</v>
+      <c r="I192" t="s">
+        <v>19</v>
+      </c>
+      <c r="J192" t="s">
+        <v>35</v>
       </c>
       <c r="K192" t="s">
-        <v>21</v>
-      </c>
-      <c r="L192" t="s">
         <v>37</v>
       </c>
-      <c r="M192" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13">
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A193">
         <v>596</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C193">
         <v>5</v>
@@ -7944,25 +6915,22 @@
       <c r="H193">
         <v>5</v>
       </c>
-      <c r="I193" t="b">
-        <v>1</v>
-      </c>
-      <c r="J193" t="b">
-        <v>0</v>
-      </c>
-      <c r="L193" t="s">
-        <v>37</v>
-      </c>
-      <c r="M193" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13">
+      <c r="I193" t="s">
+        <v>43</v>
+      </c>
+      <c r="J193" t="s">
+        <v>35</v>
+      </c>
+      <c r="K193" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A194">
         <v>573</v>
       </c>
       <c r="B194" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C194">
         <v>5</v>
@@ -7982,28 +6950,22 @@
       <c r="H194">
         <v>5</v>
       </c>
-      <c r="I194" t="b">
-        <v>1</v>
-      </c>
-      <c r="J194" t="b">
-        <v>1</v>
+      <c r="I194" t="s">
+        <v>17</v>
+      </c>
+      <c r="J194" t="s">
+        <v>35</v>
       </c>
       <c r="K194" t="s">
-        <v>19</v>
-      </c>
-      <c r="L194" t="s">
-        <v>37</v>
-      </c>
-      <c r="M194" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A195">
         <v>852</v>
       </c>
       <c r="B195" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C195">
         <v>5</v>
@@ -8023,25 +6985,19 @@
       <c r="H195">
         <v>5</v>
       </c>
-      <c r="I195" t="b">
-        <v>0</v>
-      </c>
-      <c r="J195" t="b">
-        <v>0</v>
-      </c>
-      <c r="L195" t="s">
-        <v>37</v>
-      </c>
-      <c r="M195" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13">
+      <c r="J195" t="s">
+        <v>35</v>
+      </c>
+      <c r="K195" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A196">
         <v>988</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C196">
         <v>3</v>
@@ -8061,25 +7017,19 @@
       <c r="H196">
         <v>5</v>
       </c>
-      <c r="I196" t="b">
-        <v>0</v>
-      </c>
-      <c r="J196" t="b">
-        <v>0</v>
-      </c>
-      <c r="L196" t="s">
+      <c r="J196" t="s">
+        <v>35</v>
+      </c>
+      <c r="K196" t="s">
         <v>37</v>
       </c>
-      <c r="M196" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13">
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A197">
         <v>707</v>
       </c>
       <c r="B197" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C197">
         <v>5</v>
@@ -8099,25 +7049,19 @@
       <c r="H197">
         <v>4</v>
       </c>
-      <c r="I197" t="b">
-        <v>0</v>
-      </c>
-      <c r="J197" t="b">
-        <v>0</v>
-      </c>
-      <c r="L197" t="s">
+      <c r="J197" t="s">
+        <v>35</v>
+      </c>
+      <c r="K197" t="s">
         <v>37</v>
       </c>
-      <c r="M197" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13">
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A198">
         <v>548</v>
       </c>
       <c r="B198" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -8137,25 +7081,19 @@
       <c r="H198">
         <v>4</v>
       </c>
-      <c r="I198" t="b">
-        <v>0</v>
-      </c>
-      <c r="J198" t="b">
-        <v>0</v>
-      </c>
-      <c r="L198" t="s">
-        <v>37</v>
-      </c>
-      <c r="M198" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13">
+      <c r="J198" t="s">
+        <v>35</v>
+      </c>
+      <c r="K198" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A199">
         <v>694</v>
       </c>
       <c r="B199" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C199">
         <v>5</v>
@@ -8175,25 +7113,19 @@
       <c r="H199">
         <v>5</v>
       </c>
-      <c r="I199" t="b">
-        <v>0</v>
-      </c>
-      <c r="J199" t="b">
-        <v>0</v>
-      </c>
-      <c r="L199" t="s">
-        <v>37</v>
-      </c>
-      <c r="M199" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13">
+      <c r="J199" t="s">
+        <v>35</v>
+      </c>
+      <c r="K199" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A200">
         <v>179</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C200">
         <v>4</v>
@@ -8213,25 +7145,19 @@
       <c r="H200">
         <v>5</v>
       </c>
-      <c r="I200" t="b">
-        <v>0</v>
-      </c>
-      <c r="J200" t="b">
-        <v>0</v>
-      </c>
-      <c r="L200" t="s">
+      <c r="J200" t="s">
+        <v>35</v>
+      </c>
+      <c r="K200" t="s">
         <v>37</v>
       </c>
-      <c r="M200" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13">
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A201">
         <v>216</v>
       </c>
       <c r="B201" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C201">
         <v>5</v>
@@ -8251,25 +7177,19 @@
       <c r="H201">
         <v>5</v>
       </c>
-      <c r="I201" t="b">
-        <v>0</v>
-      </c>
-      <c r="J201" t="b">
-        <v>0</v>
-      </c>
-      <c r="L201" t="s">
+      <c r="J201" t="s">
+        <v>35</v>
+      </c>
+      <c r="K201" t="s">
         <v>37</v>
       </c>
-      <c r="M201" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13">
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A202">
         <v>925</v>
       </c>
       <c r="B202" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C202">
         <v>5</v>
@@ -8289,25 +7209,19 @@
       <c r="H202">
         <v>5</v>
       </c>
-      <c r="I202" t="b">
-        <v>0</v>
-      </c>
-      <c r="J202" t="b">
-        <v>0</v>
-      </c>
-      <c r="L202" t="s">
-        <v>37</v>
-      </c>
-      <c r="M202" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="203" spans="1:13">
+      <c r="J202" t="s">
+        <v>35</v>
+      </c>
+      <c r="K202" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A203">
         <v>535</v>
       </c>
       <c r="B203" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C203">
         <v>5</v>
@@ -8327,25 +7241,19 @@
       <c r="H203">
         <v>5</v>
       </c>
-      <c r="I203" t="b">
-        <v>0</v>
-      </c>
-      <c r="J203" t="b">
-        <v>0</v>
-      </c>
-      <c r="L203" t="s">
+      <c r="J203" t="s">
+        <v>35</v>
+      </c>
+      <c r="K203" t="s">
         <v>37</v>
       </c>
-      <c r="M203" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13">
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A204">
         <v>220</v>
       </c>
       <c r="B204" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -8365,25 +7273,19 @@
       <c r="H204">
         <v>5</v>
       </c>
-      <c r="I204" t="b">
-        <v>0</v>
-      </c>
-      <c r="J204" t="b">
-        <v>0</v>
-      </c>
-      <c r="L204" t="s">
+      <c r="J204" t="s">
+        <v>35</v>
+      </c>
+      <c r="K204" t="s">
         <v>37</v>
       </c>
-      <c r="M204" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13">
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A205">
         <v>232</v>
       </c>
       <c r="B205" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C205">
         <v>4</v>
@@ -8403,25 +7305,19 @@
       <c r="H205">
         <v>5</v>
       </c>
-      <c r="I205" t="b">
-        <v>0</v>
-      </c>
-      <c r="J205" t="b">
-        <v>0</v>
-      </c>
-      <c r="L205" t="s">
+      <c r="J205" t="s">
+        <v>35</v>
+      </c>
+      <c r="K205" t="s">
         <v>37</v>
       </c>
-      <c r="M205" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13">
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A206">
         <v>326</v>
       </c>
       <c r="B206" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8441,25 +7337,19 @@
       <c r="H206">
         <v>5</v>
       </c>
-      <c r="I206" t="b">
-        <v>0</v>
-      </c>
-      <c r="J206" t="b">
-        <v>0</v>
-      </c>
-      <c r="L206" t="s">
-        <v>37</v>
-      </c>
-      <c r="M206" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="207" spans="1:13">
+      <c r="J206" t="s">
+        <v>35</v>
+      </c>
+      <c r="K206" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A207">
         <v>768</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -8479,25 +7369,22 @@
       <c r="H207">
         <v>5</v>
       </c>
-      <c r="I207" t="b">
-        <v>1</v>
-      </c>
-      <c r="J207" t="b">
-        <v>0</v>
-      </c>
-      <c r="L207" t="s">
-        <v>37</v>
-      </c>
-      <c r="M207" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="208" spans="1:13">
+      <c r="I207" t="s">
+        <v>54</v>
+      </c>
+      <c r="J207" t="s">
+        <v>35</v>
+      </c>
+      <c r="K207" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A208">
         <v>922</v>
       </c>
       <c r="B208" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C208">
         <v>4</v>
@@ -8517,25 +7404,19 @@
       <c r="H208">
         <v>5</v>
       </c>
-      <c r="I208" t="b">
-        <v>0</v>
-      </c>
-      <c r="J208" t="b">
-        <v>0</v>
-      </c>
-      <c r="L208" t="s">
-        <v>37</v>
-      </c>
-      <c r="M208" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="209" spans="1:13">
+      <c r="J208" t="s">
+        <v>35</v>
+      </c>
+      <c r="K208" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A209">
         <v>491</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8555,25 +7436,19 @@
       <c r="H209">
         <v>4</v>
       </c>
-      <c r="I209" t="b">
-        <v>0</v>
-      </c>
-      <c r="J209" t="b">
-        <v>0</v>
-      </c>
-      <c r="L209" t="s">
+      <c r="J209" t="s">
+        <v>35</v>
+      </c>
+      <c r="K209" t="s">
         <v>37</v>
       </c>
-      <c r="M209" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="210" spans="1:13">
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A210">
         <v>985</v>
       </c>
       <c r="B210" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -8593,25 +7468,22 @@
       <c r="H210">
         <v>5</v>
       </c>
-      <c r="I210" t="b">
-        <v>1</v>
-      </c>
-      <c r="J210" t="b">
-        <v>0</v>
-      </c>
-      <c r="L210" t="s">
+      <c r="I210" t="s">
+        <v>41</v>
+      </c>
+      <c r="J210" t="s">
+        <v>35</v>
+      </c>
+      <c r="K210" t="s">
         <v>37</v>
       </c>
-      <c r="M210" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="211" spans="1:13">
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A211">
         <v>778</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C211">
         <v>5</v>
@@ -8631,25 +7503,19 @@
       <c r="H211">
         <v>5</v>
       </c>
-      <c r="I211" t="b">
-        <v>0</v>
-      </c>
-      <c r="J211" t="b">
-        <v>0</v>
-      </c>
-      <c r="L211" t="s">
+      <c r="J211" t="s">
+        <v>35</v>
+      </c>
+      <c r="K211" t="s">
         <v>37</v>
       </c>
-      <c r="M211" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13">
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A212">
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C212">
         <v>5</v>
@@ -8669,25 +7535,19 @@
       <c r="H212">
         <v>5</v>
       </c>
-      <c r="I212" t="b">
-        <v>0</v>
-      </c>
-      <c r="J212" t="b">
-        <v>0</v>
-      </c>
-      <c r="L212" t="s">
-        <v>37</v>
-      </c>
-      <c r="M212" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13">
+      <c r="J212" t="s">
+        <v>35</v>
+      </c>
+      <c r="K212" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A213">
         <v>775</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C213">
         <v>5</v>
@@ -8707,25 +7567,22 @@
       <c r="H213">
         <v>5</v>
       </c>
-      <c r="I213" t="b">
-        <v>1</v>
-      </c>
-      <c r="J213" t="b">
-        <v>1</v>
-      </c>
-      <c r="L213" t="s">
-        <v>37</v>
-      </c>
-      <c r="M213" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13">
+      <c r="I213" t="s">
+        <v>39</v>
+      </c>
+      <c r="J213" t="s">
+        <v>35</v>
+      </c>
+      <c r="K213" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A214">
         <v>358</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C214">
         <v>5</v>
@@ -8745,25 +7602,22 @@
       <c r="H214">
         <v>5</v>
       </c>
-      <c r="I214" t="b">
-        <v>1</v>
-      </c>
-      <c r="J214" t="b">
-        <v>1</v>
-      </c>
-      <c r="L214" t="s">
-        <v>37</v>
-      </c>
-      <c r="M214" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13">
+      <c r="I214" t="s">
+        <v>44</v>
+      </c>
+      <c r="J214" t="s">
+        <v>35</v>
+      </c>
+      <c r="K214" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A215">
         <v>289</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C215">
         <v>5</v>
@@ -8783,25 +7637,19 @@
       <c r="H215">
         <v>4</v>
       </c>
-      <c r="I215" t="b">
-        <v>0</v>
-      </c>
-      <c r="J215" t="b">
-        <v>0</v>
-      </c>
-      <c r="L215" t="s">
-        <v>37</v>
-      </c>
-      <c r="M215" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13">
+      <c r="J215" t="s">
+        <v>35</v>
+      </c>
+      <c r="K215" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A216">
         <v>283</v>
       </c>
       <c r="B216" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C216">
         <v>5</v>
@@ -8821,25 +7669,19 @@
       <c r="H216">
         <v>5</v>
       </c>
-      <c r="I216" t="b">
-        <v>0</v>
-      </c>
-      <c r="J216" t="b">
-        <v>0</v>
-      </c>
-      <c r="L216" t="s">
+      <c r="J216" t="s">
+        <v>35</v>
+      </c>
+      <c r="K216" t="s">
         <v>37</v>
       </c>
-      <c r="M216" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13">
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A217">
         <v>910</v>
       </c>
       <c r="B217" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C217">
         <v>5</v>
@@ -8859,25 +7701,19 @@
       <c r="H217">
         <v>5</v>
       </c>
-      <c r="I217" t="b">
-        <v>0</v>
-      </c>
-      <c r="J217" t="b">
-        <v>0</v>
-      </c>
-      <c r="L217" t="s">
-        <v>37</v>
-      </c>
-      <c r="M217" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13">
+      <c r="J217" t="s">
+        <v>35</v>
+      </c>
+      <c r="K217" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A218">
         <v>255</v>
       </c>
       <c r="B218" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C218">
         <v>5</v>
@@ -8897,25 +7733,19 @@
       <c r="H218">
         <v>4</v>
       </c>
-      <c r="I218" t="b">
-        <v>1</v>
-      </c>
-      <c r="J218" t="b">
-        <v>0</v>
-      </c>
-      <c r="L218" t="s">
+      <c r="J218" t="s">
+        <v>35</v>
+      </c>
+      <c r="K218" t="s">
         <v>37</v>
       </c>
-      <c r="M218" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13">
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A219">
         <v>152</v>
       </c>
       <c r="B219" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C219">
         <v>5</v>
@@ -8935,28 +7765,22 @@
       <c r="H219">
         <v>4</v>
       </c>
-      <c r="I219" t="b">
-        <v>1</v>
-      </c>
-      <c r="J219" t="b">
-        <v>1</v>
+      <c r="I219" t="s">
+        <v>33</v>
+      </c>
+      <c r="J219" t="s">
+        <v>35</v>
       </c>
       <c r="K219" t="s">
-        <v>35</v>
-      </c>
-      <c r="L219" t="s">
-        <v>37</v>
-      </c>
-      <c r="M219" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A220">
         <v>177</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C220">
         <v>4</v>
@@ -8976,25 +7800,19 @@
       <c r="H220">
         <v>5</v>
       </c>
-      <c r="I220" t="b">
-        <v>0</v>
-      </c>
-      <c r="J220" t="b">
-        <v>0</v>
-      </c>
-      <c r="L220" t="s">
-        <v>37</v>
-      </c>
-      <c r="M220" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13">
+      <c r="J220" t="s">
+        <v>35</v>
+      </c>
+      <c r="K220" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A221">
         <v>425</v>
       </c>
       <c r="B221" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C221">
         <v>5</v>
@@ -9014,25 +7832,19 @@
       <c r="H221">
         <v>5</v>
       </c>
-      <c r="I221" t="b">
-        <v>0</v>
-      </c>
-      <c r="J221" t="b">
-        <v>0</v>
-      </c>
-      <c r="L221" t="s">
+      <c r="J221" t="s">
+        <v>35</v>
+      </c>
+      <c r="K221" t="s">
         <v>37</v>
       </c>
-      <c r="M221" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13">
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A222">
         <v>223</v>
       </c>
       <c r="B222" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C222">
         <v>5</v>
@@ -9052,25 +7864,19 @@
       <c r="H222">
         <v>5</v>
       </c>
-      <c r="I222" t="b">
-        <v>0</v>
-      </c>
-      <c r="J222" t="b">
-        <v>0</v>
-      </c>
-      <c r="L222" t="s">
-        <v>37</v>
-      </c>
-      <c r="M222" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13">
+      <c r="J222" t="s">
+        <v>35</v>
+      </c>
+      <c r="K222" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A223">
         <v>455</v>
       </c>
       <c r="B223" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C223">
         <v>5</v>
@@ -9090,25 +7896,19 @@
       <c r="H223">
         <v>4</v>
       </c>
-      <c r="I223" t="b">
-        <v>0</v>
-      </c>
-      <c r="J223" t="b">
-        <v>0</v>
-      </c>
-      <c r="L223" t="s">
-        <v>37</v>
-      </c>
-      <c r="M223" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13">
+      <c r="J223" t="s">
+        <v>35</v>
+      </c>
+      <c r="K223" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A224">
         <v>661</v>
       </c>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C224">
         <v>5</v>
@@ -9128,25 +7928,19 @@
       <c r="H224">
         <v>5</v>
       </c>
-      <c r="I224" t="b">
-        <v>0</v>
-      </c>
-      <c r="J224" t="b">
-        <v>0</v>
-      </c>
-      <c r="L224" t="s">
+      <c r="J224" t="s">
+        <v>35</v>
+      </c>
+      <c r="K224" t="s">
         <v>37</v>
       </c>
-      <c r="M224" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13">
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A225">
         <v>22</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C225">
         <v>5</v>
@@ -9166,25 +7960,22 @@
       <c r="H225">
         <v>5</v>
       </c>
-      <c r="I225" t="b">
-        <v>1</v>
-      </c>
-      <c r="J225" t="b">
-        <v>0</v>
-      </c>
-      <c r="L225" t="s">
+      <c r="I225" t="s">
+        <v>46</v>
+      </c>
+      <c r="J225" t="s">
+        <v>35</v>
+      </c>
+      <c r="K225" t="s">
         <v>37</v>
       </c>
-      <c r="M225" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13">
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A226">
         <v>421</v>
       </c>
       <c r="B226" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C226">
         <v>4</v>
@@ -9204,28 +7995,22 @@
       <c r="H226">
         <v>5</v>
       </c>
-      <c r="I226" t="b">
-        <v>0</v>
-      </c>
-      <c r="J226" t="b">
-        <v>0</v>
+      <c r="I226" t="s">
+        <v>22</v>
+      </c>
+      <c r="J226" t="s">
+        <v>35</v>
       </c>
       <c r="K226" t="s">
-        <v>24</v>
-      </c>
-      <c r="L226" t="s">
         <v>37</v>
       </c>
-      <c r="M226" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13">
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A227">
         <v>772</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C227">
         <v>5</v>
@@ -9245,25 +8030,19 @@
       <c r="H227">
         <v>5</v>
       </c>
-      <c r="I227" t="b">
-        <v>0</v>
-      </c>
-      <c r="J227" t="b">
-        <v>0</v>
-      </c>
-      <c r="L227" t="s">
+      <c r="J227" t="s">
+        <v>35</v>
+      </c>
+      <c r="K227" t="s">
         <v>37</v>
       </c>
-      <c r="M227" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13">
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A228">
         <v>654</v>
       </c>
       <c r="B228" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C228">
         <v>5</v>
@@ -9283,25 +8062,19 @@
       <c r="H228">
         <v>5</v>
       </c>
-      <c r="I228" t="b">
-        <v>0</v>
-      </c>
-      <c r="J228" t="b">
-        <v>0</v>
-      </c>
-      <c r="L228" t="s">
+      <c r="J228" t="s">
+        <v>35</v>
+      </c>
+      <c r="K228" t="s">
         <v>37</v>
       </c>
-      <c r="M228" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13">
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A229">
         <v>171</v>
       </c>
       <c r="B229" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C229">
         <v>5</v>
@@ -9321,25 +8094,22 @@
       <c r="H229">
         <v>4</v>
       </c>
-      <c r="I229" t="b">
-        <v>1</v>
-      </c>
-      <c r="J229" t="b">
-        <v>1</v>
-      </c>
-      <c r="L229" t="s">
+      <c r="I229" t="s">
+        <v>45</v>
+      </c>
+      <c r="J229" t="s">
+        <v>35</v>
+      </c>
+      <c r="K229" t="s">
         <v>37</v>
       </c>
-      <c r="M229" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13">
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A230">
         <v>477</v>
       </c>
       <c r="B230" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C230">
         <v>5</v>
@@ -9359,28 +8129,22 @@
       <c r="H230">
         <v>5</v>
       </c>
-      <c r="I230" t="b">
-        <v>1</v>
-      </c>
-      <c r="J230" t="b">
-        <v>0</v>
+      <c r="I230" t="s">
+        <v>17</v>
+      </c>
+      <c r="J230" t="s">
+        <v>35</v>
       </c>
       <c r="K230" t="s">
-        <v>19</v>
-      </c>
-      <c r="L230" t="s">
-        <v>37</v>
-      </c>
-      <c r="M230" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A231">
         <v>504</v>
       </c>
       <c r="B231" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C231">
         <v>5</v>
@@ -9400,28 +8164,22 @@
       <c r="H231">
         <v>5</v>
       </c>
-      <c r="I231" t="b">
-        <v>1</v>
-      </c>
-      <c r="J231" t="b">
-        <v>0</v>
+      <c r="I231" t="s">
+        <v>18</v>
+      </c>
+      <c r="J231" t="s">
+        <v>35</v>
       </c>
       <c r="K231" t="s">
-        <v>20</v>
-      </c>
-      <c r="L231" t="s">
-        <v>37</v>
-      </c>
-      <c r="M231" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A232">
         <v>587</v>
       </c>
       <c r="B232" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C232">
         <v>5</v>
@@ -9441,25 +8199,19 @@
       <c r="H232">
         <v>5</v>
       </c>
-      <c r="I232" t="b">
-        <v>0</v>
-      </c>
-      <c r="J232" t="b">
-        <v>0</v>
-      </c>
-      <c r="L232" t="s">
-        <v>37</v>
-      </c>
-      <c r="M232" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13">
+      <c r="J232" t="s">
+        <v>35</v>
+      </c>
+      <c r="K232" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A233">
         <v>884</v>
       </c>
       <c r="B233" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C233">
         <v>5</v>
@@ -9479,25 +8231,19 @@
       <c r="H233">
         <v>5</v>
       </c>
-      <c r="I233" t="b">
-        <v>0</v>
-      </c>
-      <c r="J233" t="b">
-        <v>0</v>
-      </c>
-      <c r="L233" t="s">
-        <v>37</v>
-      </c>
-      <c r="M233" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13">
+      <c r="J233" t="s">
+        <v>35</v>
+      </c>
+      <c r="K233" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A234">
         <v>145</v>
       </c>
       <c r="B234" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C234">
         <v>5</v>
@@ -9517,28 +8263,22 @@
       <c r="H234">
         <v>4</v>
       </c>
-      <c r="I234" t="b">
-        <v>0</v>
-      </c>
-      <c r="J234" t="b">
-        <v>0</v>
+      <c r="I234" t="s">
+        <v>22</v>
+      </c>
+      <c r="J234" t="s">
+        <v>35</v>
       </c>
       <c r="K234" t="s">
-        <v>24</v>
-      </c>
-      <c r="L234" t="s">
-        <v>37</v>
-      </c>
-      <c r="M234" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A235">
         <v>277</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C235">
         <v>5</v>
@@ -9558,25 +8298,19 @@
       <c r="H235">
         <v>5</v>
       </c>
-      <c r="I235" t="b">
-        <v>0</v>
-      </c>
-      <c r="J235" t="b">
-        <v>0</v>
-      </c>
-      <c r="L235" t="s">
-        <v>37</v>
-      </c>
-      <c r="M235" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13">
+      <c r="J235" t="s">
+        <v>35</v>
+      </c>
+      <c r="K235" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A236">
         <v>211</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C236">
         <v>5</v>
@@ -9596,25 +8330,19 @@
       <c r="H236">
         <v>5</v>
       </c>
-      <c r="I236" t="b">
-        <v>0</v>
-      </c>
-      <c r="J236" t="b">
-        <v>0</v>
-      </c>
-      <c r="L236" t="s">
+      <c r="J236" t="s">
+        <v>35</v>
+      </c>
+      <c r="K236" t="s">
         <v>37</v>
       </c>
-      <c r="M236" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13">
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A237">
         <v>857</v>
       </c>
       <c r="B237" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C237">
         <v>5</v>
@@ -9634,28 +8362,22 @@
       <c r="H237">
         <v>5</v>
       </c>
-      <c r="I237" t="b">
-        <v>0</v>
-      </c>
-      <c r="J237" t="b">
-        <v>0</v>
+      <c r="I237" t="s">
+        <v>25</v>
+      </c>
+      <c r="J237" t="s">
+        <v>35</v>
       </c>
       <c r="K237" t="s">
-        <v>27</v>
-      </c>
-      <c r="L237" t="s">
-        <v>37</v>
-      </c>
-      <c r="M237" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="238" spans="1:13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A238">
         <v>956</v>
       </c>
       <c r="B238" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C238">
         <v>5</v>
@@ -9675,28 +8397,22 @@
       <c r="H238">
         <v>5</v>
       </c>
-      <c r="I238" t="b">
-        <v>1</v>
-      </c>
-      <c r="J238" t="b">
-        <v>0</v>
+      <c r="I238" t="s">
+        <v>32</v>
+      </c>
+      <c r="J238" t="s">
+        <v>35</v>
       </c>
       <c r="K238" t="s">
-        <v>34</v>
-      </c>
-      <c r="L238" t="s">
         <v>37</v>
       </c>
-      <c r="M238" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="239" spans="1:13">
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A239">
         <v>394</v>
       </c>
       <c r="B239" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C239">
         <v>5</v>
@@ -9716,25 +8432,19 @@
       <c r="H239">
         <v>5</v>
       </c>
-      <c r="I239" t="b">
-        <v>0</v>
-      </c>
-      <c r="J239" t="b">
-        <v>0</v>
-      </c>
-      <c r="L239" t="s">
+      <c r="J239" t="s">
+        <v>35</v>
+      </c>
+      <c r="K239" t="s">
         <v>37</v>
       </c>
-      <c r="M239" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="240" spans="1:13">
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A240">
         <v>697</v>
       </c>
       <c r="B240" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C240">
         <v>5</v>
@@ -9754,25 +8464,19 @@
       <c r="H240">
         <v>5</v>
       </c>
-      <c r="I240" t="b">
-        <v>0</v>
-      </c>
-      <c r="J240" t="b">
-        <v>0</v>
-      </c>
-      <c r="L240" t="s">
-        <v>37</v>
-      </c>
-      <c r="M240" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="241" spans="1:13">
+      <c r="J240" t="s">
+        <v>35</v>
+      </c>
+      <c r="K240" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A241">
         <v>634</v>
       </c>
       <c r="B241" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C241">
         <v>5</v>
@@ -9792,25 +8496,19 @@
       <c r="H241">
         <v>4</v>
       </c>
-      <c r="I241" t="b">
-        <v>0</v>
-      </c>
-      <c r="J241" t="b">
-        <v>0</v>
-      </c>
-      <c r="L241" t="s">
-        <v>37</v>
-      </c>
-      <c r="M241" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="242" spans="1:13">
+      <c r="J241" t="s">
+        <v>35</v>
+      </c>
+      <c r="K241" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A242">
         <v>27</v>
       </c>
       <c r="B242" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C242">
         <v>5</v>
@@ -9830,25 +8528,19 @@
       <c r="H242">
         <v>5</v>
       </c>
-      <c r="I242" t="b">
-        <v>0</v>
-      </c>
-      <c r="J242" t="b">
-        <v>0</v>
-      </c>
-      <c r="L242" t="s">
-        <v>37</v>
-      </c>
-      <c r="M242" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="243" spans="1:13">
+      <c r="J242" t="s">
+        <v>35</v>
+      </c>
+      <c r="K242" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A243">
         <v>432</v>
       </c>
       <c r="B243" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C243">
         <v>5</v>
@@ -9868,28 +8560,22 @@
       <c r="H243">
         <v>5</v>
       </c>
-      <c r="I243" t="b">
-        <v>0</v>
-      </c>
-      <c r="J243" t="b">
-        <v>0</v>
+      <c r="I243" t="s">
+        <v>26</v>
+      </c>
+      <c r="J243" t="s">
+        <v>35</v>
       </c>
       <c r="K243" t="s">
-        <v>28</v>
-      </c>
-      <c r="L243" t="s">
         <v>37</v>
       </c>
-      <c r="M243" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="244" spans="1:13">
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A244">
         <v>317</v>
       </c>
       <c r="B244" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C244">
         <v>5</v>
@@ -9909,25 +8595,19 @@
       <c r="H244">
         <v>5</v>
       </c>
-      <c r="I244" t="b">
-        <v>0</v>
-      </c>
-      <c r="J244" t="b">
-        <v>0</v>
-      </c>
-      <c r="L244" t="s">
+      <c r="J244" t="s">
+        <v>35</v>
+      </c>
+      <c r="K244" t="s">
         <v>37</v>
       </c>
-      <c r="M244" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="245" spans="1:13">
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A245">
         <v>850</v>
       </c>
       <c r="B245" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C245">
         <v>5</v>
@@ -9947,25 +8627,19 @@
       <c r="H245">
         <v>5</v>
       </c>
-      <c r="I245" t="b">
-        <v>0</v>
-      </c>
-      <c r="J245" t="b">
-        <v>0</v>
-      </c>
-      <c r="L245" t="s">
-        <v>37</v>
-      </c>
-      <c r="M245" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="246" spans="1:13">
+      <c r="J245" t="s">
+        <v>35</v>
+      </c>
+      <c r="K245" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A246">
         <v>197</v>
       </c>
       <c r="B246" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C246">
         <v>4</v>
@@ -9985,28 +8659,22 @@
       <c r="H246">
         <v>5</v>
       </c>
-      <c r="I246" t="b">
-        <v>1</v>
-      </c>
-      <c r="J246" t="b">
-        <v>1</v>
+      <c r="I246" t="s">
+        <v>34</v>
+      </c>
+      <c r="J246" t="s">
+        <v>35</v>
       </c>
       <c r="K246" t="s">
         <v>36</v>
       </c>
-      <c r="L246" t="s">
-        <v>37</v>
-      </c>
-      <c r="M246" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="247" spans="1:13">
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A247">
         <v>97</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C247">
         <v>5</v>
@@ -10026,25 +8694,19 @@
       <c r="H247">
         <v>5</v>
       </c>
-      <c r="I247" t="b">
-        <v>0</v>
-      </c>
-      <c r="J247" t="b">
-        <v>0</v>
-      </c>
-      <c r="L247" t="s">
+      <c r="J247" t="s">
+        <v>35</v>
+      </c>
+      <c r="K247" t="s">
         <v>37</v>
       </c>
-      <c r="M247" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="248" spans="1:13">
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A248">
         <v>303</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C248">
         <v>5</v>
@@ -10064,25 +8726,19 @@
       <c r="H248">
         <v>4</v>
       </c>
-      <c r="I248" t="b">
-        <v>1</v>
-      </c>
-      <c r="J248" t="b">
-        <v>0</v>
-      </c>
-      <c r="L248" t="s">
-        <v>37</v>
-      </c>
-      <c r="M248" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="249" spans="1:13">
+      <c r="J248" t="s">
+        <v>35</v>
+      </c>
+      <c r="K248" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A249">
         <v>935</v>
       </c>
       <c r="B249" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C249">
         <v>5</v>
@@ -10102,28 +8758,22 @@
       <c r="H249">
         <v>5</v>
       </c>
-      <c r="I249" t="b">
-        <v>0</v>
-      </c>
-      <c r="J249" t="b">
-        <v>0</v>
+      <c r="I249" t="s">
+        <v>19</v>
+      </c>
+      <c r="J249" t="s">
+        <v>35</v>
       </c>
       <c r="K249" t="s">
-        <v>21</v>
-      </c>
-      <c r="L249" t="s">
-        <v>37</v>
-      </c>
-      <c r="M249" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="250" spans="1:13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A250">
         <v>65</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C250">
         <v>5</v>
@@ -10143,25 +8793,19 @@
       <c r="H250">
         <v>5</v>
       </c>
-      <c r="I250" t="b">
-        <v>0</v>
-      </c>
-      <c r="J250" t="b">
-        <v>0</v>
-      </c>
-      <c r="L250" t="s">
-        <v>37</v>
-      </c>
-      <c r="M250" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="251" spans="1:13">
+      <c r="J250" t="s">
+        <v>35</v>
+      </c>
+      <c r="K250" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A251">
         <v>656</v>
       </c>
       <c r="B251" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C251">
         <v>5</v>
@@ -10181,20 +8825,15 @@
       <c r="H251">
         <v>5</v>
       </c>
-      <c r="I251" t="b">
-        <v>0</v>
-      </c>
-      <c r="J251" t="b">
-        <v>0</v>
-      </c>
-      <c r="L251" t="s">
-        <v>37</v>
-      </c>
-      <c r="M251" t="s">
-        <v>40</v>
+      <c r="J251" t="s">
+        <v>35</v>
+      </c>
+      <c r="K251" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>